--- a/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="487">
   <si>
     <t>#</t>
   </si>
@@ -502,9 +502,6 @@
   </si>
   <si>
     <t>TVS DIODE 5V 9.8V SOD923</t>
-  </si>
-  <si>
-    <t>TVS SURGE PROTECTOR 1-CH 3.3V</t>
   </si>
   <si>
     <t>TVS DIODE 28VWM 45.4VC SMB</t>
@@ -757,9 +754,6 @@
     <t>SOD-923.</t>
   </si>
   <si>
-    <t>SOD-123</t>
-  </si>
-  <si>
     <t>SMB_</t>
   </si>
   <si>
@@ -970,9 +964,6 @@
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
-    <t>AZ3003-01G</t>
-  </si>
-  <si>
     <t>SMBJ28A-13-F</t>
   </si>
   <si>
@@ -1186,9 +1177,6 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
-    <t>Amazing</t>
-  </si>
-  <si>
     <t>Diodes</t>
   </si>
   <si>
@@ -1478,6 +1466,21 @@
   </si>
   <si>
     <t>DO NOT PLACE</t>
+  </si>
+  <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>68000-103HLF</t>
+  </si>
+  <si>
+    <t>Amphenol</t>
   </si>
 </sst>
 </file>
@@ -1697,9 +1700,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1714,6 +1714,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2026,9 +2029,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2045,22 +2048,22 @@
         <v>133</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2079,16 +2082,16 @@
         <v>134</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
@@ -2111,16 +2114,16 @@
         <v>135</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="J4" s="9">
         <v>2</v>
@@ -2143,16 +2146,16 @@
         <v>136</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J5" s="7">
         <v>9</v>
@@ -2175,16 +2178,16 @@
         <v>137</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -2207,24 +2210,24 @@
         <v>138</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J7" s="7">
         <v>11</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" s="19" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
+    <row r="8" spans="1:11" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2232,29 +2235,29 @@
       <c r="C8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J8" s="15">
-        <v>2</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>485</v>
+      <c r="F8" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="J8" s="14">
+        <v>2</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2273,16 +2276,16 @@
         <v>140</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="J9" s="7">
         <v>2</v>
@@ -2305,16 +2308,16 @@
         <v>141</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
@@ -2337,16 +2340,16 @@
         <v>142</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J11" s="7">
         <v>2</v>
@@ -2369,16 +2372,16 @@
         <v>139</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -2401,16 +2404,16 @@
         <v>143</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -2433,16 +2436,16 @@
         <v>144</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="J14" s="9">
         <v>7</v>
@@ -2465,16 +2468,16 @@
         <v>145</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J15" s="7">
         <v>8</v>
@@ -2497,16 +2500,16 @@
         <v>146</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J16" s="9">
         <v>4</v>
@@ -2529,16 +2532,16 @@
         <v>147</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -2561,16 +2564,16 @@
         <v>148</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J18" s="9">
         <v>2</v>
@@ -2586,29 +2589,29 @@
       <c r="C19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J19" s="15">
+      <c r="F19" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="J19" s="14">
         <v>8</v>
       </c>
-      <c r="K19" s="17" t="s">
-        <v>485</v>
+      <c r="K19" s="16" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2627,16 +2630,16 @@
         <v>150</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J20" s="9">
         <v>2</v>
@@ -2659,16 +2662,16 @@
         <v>151</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="J21" s="7">
         <v>3</v>
@@ -2691,16 +2694,16 @@
         <v>152</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="J22" s="9">
         <v>1</v>
@@ -2723,16 +2726,16 @@
         <v>153</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="J23" s="7">
         <v>1</v>
@@ -2755,16 +2758,16 @@
         <v>154</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J24" s="9">
         <v>2</v>
@@ -2787,16 +2790,16 @@
         <v>155</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
@@ -2819,16 +2822,16 @@
         <v>156</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="J26" s="9">
         <v>2</v>
@@ -2851,16 +2854,16 @@
         <v>157</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J27" s="7">
         <v>1</v>
@@ -2883,16 +2886,16 @@
         <v>158</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
@@ -2915,16 +2918,16 @@
         <v>159</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="J29" s="7">
         <v>1</v>
@@ -2947,23 +2950,23 @@
         <v>160</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J30" s="9">
         <v>4</v>
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
@@ -2975,20 +2978,20 @@
       <c r="D31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="H31" s="7" t="s">
+      <c r="E31" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>388</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J31" s="7">
         <v>2</v>
@@ -3008,19 +3011,19 @@
         <v>56</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -3040,19 +3043,19 @@
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -3072,19 +3075,19 @@
         <v>58</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J34" s="9">
         <v>8</v>
@@ -3104,19 +3107,19 @@
         <v>59</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J35" s="7">
         <v>1</v>
@@ -3136,19 +3139,19 @@
         <v>60</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J36" s="9">
         <v>1</v>
@@ -3168,19 +3171,19 @@
         <v>61</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J37" s="7">
         <v>8</v>
@@ -3200,19 +3203,19 @@
         <v>62</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J38" s="9">
         <v>2</v>
@@ -3232,19 +3235,19 @@
         <v>63</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="J39" s="7">
         <v>2</v>
@@ -3264,19 +3267,19 @@
         <v>64</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J40" s="9">
         <v>2</v>
@@ -3296,19 +3299,19 @@
         <v>65</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J41" s="7">
         <v>4</v>
@@ -3328,19 +3331,19 @@
         <v>66</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J42" s="9">
         <v>1</v>
@@ -3360,19 +3363,19 @@
         <v>67</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J43" s="7">
         <v>2</v>
@@ -3392,15 +3395,19 @@
         <v>68</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="G44" s="10"/>
-      <c r="H44" s="9"/>
+        <v>253</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>486</v>
+      </c>
       <c r="I44" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
@@ -3420,19 +3427,19 @@
         <v>69</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J45" s="7">
         <v>1</v>
@@ -3452,19 +3459,19 @@
         <v>70</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J46" s="9">
         <v>1</v>
@@ -3484,19 +3491,19 @@
         <v>71</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G47" s="8">
         <v>1715721</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J47" s="7">
         <v>5</v>
@@ -3516,19 +3523,19 @@
         <v>72</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J48" s="9">
         <v>1</v>
@@ -3548,17 +3555,17 @@
         <v>73</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
@@ -3578,19 +3585,19 @@
         <v>74</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J50" s="9">
         <v>1</v>
@@ -3610,19 +3617,19 @@
         <v>75</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J51" s="7">
         <v>3</v>
@@ -3642,19 +3649,19 @@
         <v>76</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J52" s="9">
         <v>1</v>
@@ -3674,19 +3681,19 @@
         <v>77</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J53" s="7">
         <v>1</v>
@@ -3706,19 +3713,19 @@
         <v>78</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J54" s="9">
         <v>1</v>
@@ -3738,19 +3745,19 @@
         <v>79</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
@@ -3770,19 +3777,19 @@
         <v>80</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J56" s="9">
         <v>1</v>
@@ -3802,19 +3809,19 @@
         <v>81</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J57" s="7">
         <v>4</v>
@@ -3834,19 +3841,19 @@
         <v>82</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J58" s="9">
         <v>1</v>
@@ -3866,19 +3873,19 @@
         <v>83</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -3898,19 +3905,19 @@
         <v>84</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J60" s="9">
         <v>1</v>
@@ -3930,19 +3937,19 @@
         <v>85</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="J61" s="7">
         <v>4</v>
@@ -3962,19 +3969,19 @@
         <v>86</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="J62" s="9">
         <v>3</v>
@@ -3994,19 +4001,19 @@
         <v>87</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="J63" s="7">
         <v>17</v>
@@ -4022,29 +4029,29 @@
       <c r="C64" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E64" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="I64" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J64" s="15">
-        <v>2</v>
-      </c>
-      <c r="K64" s="17" t="s">
-        <v>485</v>
+      <c r="E64" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="J64" s="14">
+        <v>2</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4060,19 +4067,19 @@
         <v>89</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J65" s="7">
         <v>2</v>
@@ -4092,19 +4099,19 @@
         <v>90</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="J66" s="9">
         <v>1</v>
@@ -4124,19 +4131,19 @@
         <v>91</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J67" s="7">
         <v>1</v>
@@ -4156,19 +4163,19 @@
         <v>92</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J68" s="9">
         <v>1</v>
@@ -4188,19 +4195,19 @@
         <v>93</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J69" s="7">
         <v>1</v>
@@ -4220,19 +4227,19 @@
         <v>94</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="J70" s="9">
         <v>1</v>
@@ -4252,17 +4259,17 @@
         <v>95</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="8" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="J71" s="7">
         <v>2</v>
@@ -4282,19 +4289,19 @@
         <v>96</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J72" s="9">
         <v>2</v>
@@ -4314,19 +4321,19 @@
         <v>97</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J73" s="7">
         <v>13</v>
@@ -4346,19 +4353,19 @@
         <v>98</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="J74" s="9">
         <v>8</v>
@@ -4378,19 +4385,19 @@
         <v>99</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="J75" s="7">
         <v>2</v>
@@ -4410,19 +4417,19 @@
         <v>100</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
@@ -4438,29 +4445,29 @@
       <c r="C77" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E77" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="F77" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="H77" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="I77" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J77" s="15">
-        <v>1</v>
-      </c>
-      <c r="K77" s="17" t="s">
-        <v>485</v>
+      <c r="E77" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="I77" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="J77" s="14">
+        <v>1</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4476,19 +4483,19 @@
         <v>102</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J78" s="9">
         <v>2</v>
@@ -4508,19 +4515,19 @@
         <v>103</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="J79" s="7">
         <v>12</v>
@@ -4540,19 +4547,19 @@
         <v>104</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J80" s="9">
         <v>2</v>
@@ -4572,19 +4579,19 @@
         <v>105</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J81" s="7">
         <v>1</v>
@@ -4604,19 +4611,19 @@
         <v>106</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J82" s="9">
         <v>6</v>
@@ -4636,19 +4643,19 @@
         <v>107</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="J83" s="7">
         <v>1</v>
@@ -4668,19 +4675,19 @@
         <v>108</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="J84" s="9">
         <v>1</v>
@@ -4700,19 +4707,19 @@
         <v>109</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J85" s="7">
         <v>2</v>
@@ -4732,19 +4739,19 @@
         <v>110</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J86" s="9">
         <v>1</v>
@@ -4764,19 +4771,19 @@
         <v>111</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="J87" s="7">
         <v>1</v>
@@ -4796,19 +4803,19 @@
         <v>112</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J88" s="9">
         <v>1</v>
@@ -4828,19 +4835,19 @@
         <v>113</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="J89" s="7">
         <v>1</v>
@@ -4860,19 +4867,19 @@
         <v>114</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="J90" s="9">
         <v>3</v>
@@ -4892,19 +4899,19 @@
         <v>115</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J91" s="7">
         <v>3</v>
@@ -4924,19 +4931,19 @@
         <v>116</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J92" s="9">
         <v>4</v>
@@ -4956,19 +4963,19 @@
         <v>117</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J93" s="7">
         <v>1</v>
@@ -4988,19 +4995,19 @@
         <v>118</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J94" s="9">
         <v>1</v>
@@ -5020,19 +5027,19 @@
         <v>119</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J95" s="7">
         <v>1</v>
@@ -5052,19 +5059,19 @@
         <v>120</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J96" s="9">
         <v>1</v>
@@ -5084,19 +5091,19 @@
         <v>121</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J97" s="7">
         <v>1</v>
@@ -5116,19 +5123,19 @@
         <v>122</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J98" s="9">
         <v>1</v>
@@ -5148,19 +5155,19 @@
         <v>123</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J99" s="7">
         <v>2</v>
@@ -5180,19 +5187,19 @@
         <v>124</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J100" s="9">
         <v>1</v>
@@ -5212,19 +5219,19 @@
         <v>125</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J101" s="7">
         <v>1</v>
@@ -5244,19 +5251,19 @@
         <v>126</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J102" s="9">
         <v>1</v>
@@ -5276,19 +5283,19 @@
         <v>127</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J103" s="7">
         <v>1</v>
@@ -5308,19 +5315,19 @@
         <v>128</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J104" s="9">
         <v>1</v>
@@ -5336,29 +5343,29 @@
       <c r="C105" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D105" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E105" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="F105" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="G105" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="H105" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="I105" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J105" s="15">
-        <v>1</v>
-      </c>
-      <c r="K105" s="17" t="s">
-        <v>485</v>
+      <c r="E105" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="G105" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="J105" s="14">
+        <v>1</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5374,19 +5381,19 @@
         <v>130</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J106" s="9">
         <v>1</v>
@@ -5406,19 +5413,19 @@
         <v>131</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="J107" s="7">
         <v>1</v>
@@ -5438,19 +5445,19 @@
         <v>132</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="J108" s="9">
         <v>1</v>

--- a/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="530">
   <si>
     <t>#</t>
   </si>
@@ -30,9 +30,18 @@
     <t>Capacitor</t>
   </si>
   <si>
+    <t>Capacitors</t>
+  </si>
+  <si>
+    <t>(TVS/ESD)</t>
+  </si>
+  <si>
     <t>Diode</t>
   </si>
   <si>
+    <t>TVS Diodes</t>
+  </si>
+  <si>
     <t>Fuse</t>
   </si>
   <si>
@@ -51,15 +60,21 @@
     <t>Male Header</t>
   </si>
   <si>
+    <t>Fuse Holder</t>
+  </si>
+  <si>
     <t>Terminal Blocks</t>
   </si>
   <si>
+    <t>Connectors (RJ45 RJ11)</t>
+  </si>
+  <si>
+    <t>RJ45 Connector</t>
+  </si>
+  <si>
     <t>FFC/FPC Connector</t>
   </si>
   <si>
-    <t>RJ45 Connector</t>
-  </si>
-  <si>
     <t>Terminal Block</t>
   </si>
   <si>
@@ -84,6 +99,9 @@
     <t>Switch</t>
   </si>
   <si>
+    <t>DIP Switches</t>
+  </si>
+  <si>
     <t>Module</t>
   </si>
   <si>
@@ -93,7 +111,7 @@
     <t>IC</t>
   </si>
   <si>
-    <t>LED Driver</t>
+    <t>TVS Diode</t>
   </si>
   <si>
     <t>Crystal</t>
@@ -102,72 +120,63 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C4</t>
-  </si>
-  <si>
-    <t>C2, C5</t>
-  </si>
-  <si>
-    <t>C3, C6, C11, C22, C23, C28, C29, C30, C58</t>
-  </si>
-  <si>
-    <t>C7, C37</t>
-  </si>
-  <si>
-    <t>C8, C14, C16, C39, C40, C42, C43, C46, C47, C48, C50</t>
-  </si>
-  <si>
-    <t>C9, C10</t>
-  </si>
-  <si>
-    <t>C12, C13</t>
-  </si>
-  <si>
-    <t>C15, C19</t>
-  </si>
-  <si>
-    <t>C17, C18</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21, C24</t>
-  </si>
-  <si>
-    <t>C25, C31, C32, C33, C34, C35, C36</t>
-  </si>
-  <si>
-    <t>C26, C27, C70, C71, C72, C73, C74, C75</t>
-  </si>
-  <si>
-    <t>C38, C41, C44, C49</t>
-  </si>
-  <si>
-    <t>C45</t>
-  </si>
-  <si>
-    <t>C51, C52</t>
-  </si>
-  <si>
-    <t>C53, C54, C55, C56, C59, C60, C61, C62</t>
-  </si>
-  <si>
-    <t>C57, C63</t>
-  </si>
-  <si>
-    <t>C64, C65, C66</t>
+    <t>C1, C8</t>
+  </si>
+  <si>
+    <t>C2, C69, C76</t>
+  </si>
+  <si>
+    <t>C3, C5, C12, C13, C28, C29, C30, C33, C34, C36, C37, C40, C58</t>
+  </si>
+  <si>
+    <t>C4, C6</t>
+  </si>
+  <si>
+    <t>C7, C11, C89, C90</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C10, C14, C15, C16, C24, C49, C50, C51, C52, C53, C54, C55, C56, C57, C59, C62, C63, C64, C88, C96</t>
+  </si>
+  <si>
+    <t>C17, C27, C70, C71, C72, C73, C74, C75</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C19, C20, C21</t>
+  </si>
+  <si>
+    <t>C22, C32, C39</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C25, C31, C68</t>
+  </si>
+  <si>
+    <t>C35, C38</t>
+  </si>
+  <si>
+    <t>C41, C42, C43, C44, C45, C46, C47, C48</t>
+  </si>
+  <si>
+    <t>C60</t>
+  </si>
+  <si>
+    <t>C61</t>
+  </si>
+  <si>
+    <t>C65, C66, C85, C86, C91, C92, C93, C94</t>
   </si>
   <si>
     <t>C67</t>
   </si>
   <si>
-    <t>C68</t>
-  </si>
-  <si>
-    <t>C69, C76</t>
-  </si>
-  <si>
     <t>C77, C78</t>
   </si>
   <si>
@@ -183,37 +192,49 @@
     <t>C84</t>
   </si>
   <si>
-    <t>D1, D2, D16, D17</t>
-  </si>
-  <si>
-    <t>D3, D4</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>D7, D8, D9, D10, D11, D12, D13, D14</t>
-  </si>
-  <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>D18</t>
-  </si>
-  <si>
-    <t>F1, F2, F3, F4, F5, F6, F7, F8</t>
-  </si>
-  <si>
-    <t>FB1, FB2</t>
+    <t>C87, C95</t>
+  </si>
+  <si>
+    <t>D1, D2, D3, D4</t>
+  </si>
+  <si>
+    <t>D5, D6</t>
+  </si>
+  <si>
+    <t>D7, D8, D9, D10, D11, D12, D13, D14, D15, D16</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>D20, D22</t>
+  </si>
+  <si>
+    <t>D21, D23</t>
+  </si>
+  <si>
+    <t>D24, D29, D30</t>
+  </si>
+  <si>
+    <t>D25, D26, D27, D28</t>
+  </si>
+  <si>
+    <t>F1, F2, F3, F4, F7, F8, F9, F10</t>
+  </si>
+  <si>
+    <t>F5, F6</t>
+  </si>
+  <si>
+    <t>FB1, FB2, FB5, FB6, FB7, FB8, FB9</t>
   </si>
   <si>
     <t>FB3, FB4</t>
   </si>
   <si>
-    <t>J1, J8</t>
+    <t>J1, J7</t>
   </si>
   <si>
     <t>J2, J4, J5, J6</t>
@@ -222,9 +243,6 @@
     <t>J3</t>
   </si>
   <si>
-    <t>J7, J12</t>
-  </si>
-  <si>
     <t>J9</t>
   </si>
   <si>
@@ -234,19 +252,25 @@
     <t>J11</t>
   </si>
   <si>
-    <t>J13, J22, J23, J26, J27</t>
-  </si>
-  <si>
-    <t>J16</t>
-  </si>
-  <si>
-    <t>J17</t>
-  </si>
-  <si>
-    <t>J18</t>
-  </si>
-  <si>
-    <t>J19, J20, J21</t>
+    <t>J12</t>
+  </si>
+  <si>
+    <t>J13</t>
+  </si>
+  <si>
+    <t>J14</t>
+  </si>
+  <si>
+    <t>J15</t>
+  </si>
+  <si>
+    <t>J17, J19, J20, J23, J26, J27, J28</t>
+  </si>
+  <si>
+    <t>J18, J22</t>
+  </si>
+  <si>
+    <t>J21, J34, J35</t>
   </si>
   <si>
     <t>J24</t>
@@ -255,19 +279,22 @@
     <t>J25</t>
   </si>
   <si>
+    <t>J29, J30, J31, J32, J33</t>
+  </si>
+  <si>
+    <t>J36</t>
+  </si>
+  <si>
     <t>L1</t>
   </si>
   <si>
     <t>L2</t>
   </si>
   <si>
-    <t>L3</t>
-  </si>
-  <si>
     <t>LED1, LED2, LED3, LED5</t>
   </si>
   <si>
-    <t>LED4</t>
+    <t>LED4, LED?</t>
   </si>
   <si>
     <t>Q1</t>
@@ -276,75 +303,66 @@
     <t>Q2</t>
   </si>
   <si>
-    <t>R1, R2, R9, R10</t>
-  </si>
-  <si>
-    <t>R3, R11, R85</t>
-  </si>
-  <si>
-    <t>R4, R5, R6, R7, R8, R12, R19, R48, R53, R55, R56, R57, R64, R73, R81, R83, R91</t>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>R1, R2, R15, R16</t>
+  </si>
+  <si>
+    <t>R3, R17, R85</t>
+  </si>
+  <si>
+    <t>R4, R5, R6, R7, R8, R20, R25, R32, R33, R34, R35, R36, R39, R40, R41, R63, R64, R73, R81, R83, R91, R92, R102, R144, R157, R165, R166, R167, R168</t>
+  </si>
+  <si>
+    <t>R9, R12</t>
+  </si>
+  <si>
+    <t>R10, R11, R21, R22, R103, R104, R105, R106, R107, R116, R122, R123, R124, R125, R126, R127, R128, R129, R130, R131, R140, R141, R159, R161, R162</t>
   </si>
   <si>
     <t>R13, R14</t>
   </si>
   <si>
-    <t>R15, R16</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>R22</t>
-  </si>
-  <si>
-    <t>R23, R25</t>
-  </si>
-  <si>
-    <t>R24, R89</t>
-  </si>
-  <si>
-    <t>R26, R27, R28, R29, R30, R34, R37, R38, R39, R40, R41, R45, R51</t>
-  </si>
-  <si>
-    <t>R31, R32, R33, R35, R42, R43, R44, R46</t>
-  </si>
-  <si>
-    <t>R36, R47</t>
-  </si>
-  <si>
-    <t>R49</t>
-  </si>
-  <si>
-    <t>R50</t>
-  </si>
-  <si>
-    <t>R52, R54</t>
-  </si>
-  <si>
-    <t>R58, R59, R60, R61, R66, R67, R68, R69, R77, R78, R80, R82</t>
-  </si>
-  <si>
-    <t>R62, R70</t>
-  </si>
-  <si>
-    <t>R63</t>
-  </si>
-  <si>
-    <t>R65, R71, R74, R75, R76, R79</t>
+    <t>R18, R19</t>
+  </si>
+  <si>
+    <t>R23, R24, R26, R27, R28, R29, R30, R31, R74, R75, R76, R79, R101</t>
+  </si>
+  <si>
+    <t>R37, R38, R49, R50, R52, R53, R57, R58, R60, R62, R65, R66, R67, R68, R69, R70, R71, R93, R94, R95, R96, R98, R99, R100, R108, R109, R111, R114, R115, R118, R132, R133, R138, R139</t>
+  </si>
+  <si>
+    <t>R42</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t>R47, R55</t>
+  </si>
+  <si>
+    <t>R48, R54, R56, R61</t>
+  </si>
+  <si>
+    <t>R51, R59</t>
   </si>
   <si>
     <t>R72</t>
   </si>
   <si>
+    <t>R77, R78, R80, R82, R145, R146, R147, R148, R151, R152, R153, R154</t>
+  </si>
+  <si>
     <t>R84</t>
   </si>
   <si>
@@ -354,24 +372,45 @@
     <t>R87</t>
   </si>
   <si>
-    <t>R90</t>
-  </si>
-  <si>
-    <t>R93</t>
-  </si>
-  <si>
-    <t>R94</t>
+    <t>R97</t>
+  </si>
+  <si>
+    <t>R110, R112, R113, R117, R120, R121, R134, R135, R136, R137</t>
+  </si>
+  <si>
+    <t>R119, R142, R143</t>
+  </si>
+  <si>
+    <t>R149, R155</t>
+  </si>
+  <si>
+    <t>R150, R160, R163, R164</t>
+  </si>
+  <si>
+    <t>R156</t>
+  </si>
+  <si>
+    <t>R158</t>
+  </si>
+  <si>
+    <t>R169</t>
+  </si>
+  <si>
+    <t>R?</t>
   </si>
   <si>
     <t>RN1, RN2, RN3</t>
   </si>
   <si>
-    <t>SW1, SW6, SW7</t>
+    <t>SW1, SW6, SW8</t>
   </si>
   <si>
     <t>SW2, SW3, SW4, SW5</t>
   </si>
   <si>
+    <t>SW7</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
@@ -387,16 +426,13 @@
     <t>U5</t>
   </si>
   <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>U7, U9</t>
+    <t>U7</t>
   </si>
   <si>
     <t>U8</t>
   </si>
   <si>
-    <t>U10</t>
+    <t>U9, U10</t>
   </si>
   <si>
     <t>U11</t>
@@ -408,6 +444,18 @@
     <t>U13</t>
   </si>
   <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>U15, U16, U17</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
     <t>X1</t>
   </si>
   <si>
@@ -426,28 +474,40 @@
     <t>CAP CER 4700PF 50V C0G/NPO 0603</t>
   </si>
   <si>
-    <t>CAP CER 4.7UF 50V X5R 0805</t>
+    <t>CAP CER 10UF 16V X5R 0603</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 16V X7R 0402</t>
   </si>
   <si>
+    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 30PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
     <t>CAP CER 4.7UF 10V X5R 0402</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 50V X7R 0402</t>
   </si>
   <si>
-    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 20PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
-    <t>100uF 10V 55mA@120Hz ±20% SMD,D6.3xL5.4mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
-  </si>
-  <si>
-    <t>CAP CER 10UF 25V X5R 0603</t>
+    <t>CAP CER 0.1UF 50V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 47PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
+    <t>CAP ALUM 220UF 20% 50V SMD</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 16V X5R 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 50V X5R 1206</t>
+  </si>
+  <si>
+    <t>CAP CER 22UF 25V X5R 0805</t>
   </si>
   <si>
     <t>CAP CER 4700PF 50V X7R 0402</t>
@@ -456,73 +516,70 @@
     <t>CAP CER 0.1UF 100V X5R 0402</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 50V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 1UF 10V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 470PF 50V X7R 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 18PF 50V C0G/NP0 0402</t>
+    <t>CAP CER 1UF 16V X5R 0402</t>
+  </si>
+  <si>
+    <t>50V 470pF ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
   </si>
   <si>
     <t>CAP CER 10PF 50V C0G/NP0 0402</t>
   </si>
   <si>
+    <t>CAP CER 22UF 35V X5R 0805</t>
+  </si>
+  <si>
+    <t>50V 6.8nF X7R ±10% 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 10000PF 50V C0G/NPO 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 0.022UF 50V X7R 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 12PF 50V C0G/NPO 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 10V X5R 0603</t>
+  </si>
+  <si>
     <t>CAP CER 0.022UF 16V X7R 0402</t>
   </si>
   <si>
-    <t>CAP ALUM 220UF 20% 50V SMD</t>
-  </si>
-  <si>
-    <t>CAP CER 22UF 35V X5R 0805</t>
-  </si>
-  <si>
-    <t>CAP CER 22UF 25V X5R 0805</t>
-  </si>
-  <si>
-    <t>CAP CER 10UF 16V X5R 0603</t>
-  </si>
-  <si>
-    <t>50V 6.8nF X7R ±10% 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 10000PF 50V C0G/NPO 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 0.022UF 50V X7R 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 12PF 50V C0G/NPO 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 10V X5R 0603</t>
-  </si>
-  <si>
     <t>TVS DIODE 5V 9.8V SOD923</t>
   </si>
   <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>±5% Single 3.1V~3.5V 300mW 3.3V SOD-323 Zener Diodes ROHS</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 60V 5A SMA</t>
+  </si>
+  <si>
     <t>TVS DIODE 28VWM 45.4VC SMB</t>
   </si>
   <si>
     <t>TVS DIODE 5VWM 6.3VC DSN0603-2</t>
   </si>
   <si>
-    <t>SMB(DO-214AA) TVS ROHS</t>
-  </si>
-  <si>
-    <t>DIODE SCHOTTKY 60V 5A SMA</t>
-  </si>
-  <si>
-    <t>40V 500mV@2A 2A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
+    <t>TVS DIODE 24VWM 40VC SOT23-3</t>
+  </si>
+  <si>
+    <t>SOT-23 TVS ROHS</t>
+  </si>
+  <si>
+    <t>TVS DIODE 8VWM 13.6VC DO214AA</t>
+  </si>
+  <si>
+    <t>60V 100mA 40A 300mA 1812 Resettable Fuses ROHS</t>
   </si>
   <si>
     <t>9V 200mA 100A 500mA 0805 Resettable Fuses ROHS</t>
   </si>
   <si>
-    <t>FERRITE BEAD 10 OHM 0402 1LN</t>
+    <t>FERRITE BEAD 220 OHM 0603 1LN</t>
   </si>
   <si>
     <t>100mΩ ±25% 300Ω@100MHz 0805 Ferrite Beads ROHS</t>
@@ -537,47 +594,52 @@
     <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
+    <t>Gold 250V 3A Policy 2.5mm 9P 260℃ -40℃~+105℃ 2.54mm Single Row Black Brass 1x9P 2.54mm Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 3POS 2.54MM</t>
+  </si>
+  <si>
+    <t>Gold 250V 3A Straight Square Pins 2.5mm 5P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x5P Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
     <t>Gold 250V 3A Straight Square Pins 2.5mm 4P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x4P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
-    <t>CONN HEADER VERT 3POS 2.54MM</t>
-  </si>
-  <si>
-    <t>Gold 250V 3A Straight Square Pins 2.5mm 6P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x6P Plugin,P=2.54mm Pin Headers ROHS</t>
-  </si>
-  <si>
-    <t>Gold 250V 3A Square Pins 2.5mm 12P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 2.54mm 1x12P Plugin,P=2.54mm Pin Headers ROHS</t>
+    <t>CONN HEADER VERT 3POS 2.5MM</t>
+  </si>
+  <si>
+    <t>FUSE HOLDER BLADE 80V PCB</t>
   </si>
   <si>
     <t>TERM BLK 2P SIDE ENT 5.08MM PCB</t>
   </si>
   <si>
-    <t>-55℃~+85℃ Clamshell 45P Bottom Contact Surface Mount，Right Angle 0.3mm SMD,P=0.3mm,Surface Mount，Right Angle FFC/FPC Connectors ROHS</t>
-  </si>
-  <si>
-    <t>1x4P 1 2mm Male pin 4 -25℃~+85℃ 2A Surface Mount SMD,P=2mm Wire To Board / Wire To Wire Connector ROHS_x000D_
-C3029442</t>
+    <t>Gold 250V 3A Straight Square Pins 2.5mm 2P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x2P Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>RJ45Receptacle Unshielded 1 Bend insert 260℃ Gold Phosphor Bronze Without LED -40℃~+85℃ Plugin Ethernet Connectors / Modular Connectors (RJ45 RJ11) ROHS</t>
+  </si>
+  <si>
+    <t>RJ45 RJReceptacle 1 WithLED Plugin Ethernet Connectors/Modular Connectors (RJ45 RJ11) ROHS</t>
+  </si>
+  <si>
+    <t>Slide Lock 32P Contact,Top Surface Mount，Right Angle 0.5mm SMD,P=0.5mm,Surface Mount，Right Angle FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 4POS 2.5MM</t>
+  </si>
+  <si>
+    <t>1x3P 18A -40℃~+105℃ 250V Black 12~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
   </si>
   <si>
     <t>M4 Plugin PCB Welding Terminal ROHS</t>
   </si>
   <si>
-    <t>RJ45 RJReceptacle 1 WithLED Plugin Ethernet Connectors/Modular Connectors (RJ45 RJ11) ROHS</t>
-  </si>
-  <si>
-    <t>Tin 1x2P Corner pin Three sides 2 1 9.5mm -40℃~+105℃ 20A 300V Black 10~22 Copper Alloy 0.5~4 Plugin,P=9.5mm Barrier Terminal Blocks ROHS</t>
-  </si>
-  <si>
-    <t>1x3P 18A -40℃~+105℃ 250V Green 14~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
-  </si>
-  <si>
     <t>FERRITE BEAD 600 OHM 0402 1LN</t>
   </si>
   <si>
-    <t>8A 4.7uH ±20% SMD,10x10.1mm Power Inductors ROHS</t>
-  </si>
-  <si>
-    <t>1.7A 15uH Molding Choke ±20% 2.2A SMD,5.2x5.4mm Power Inductors ROHS</t>
+    <t>FIXED IND 6.8UH 5A 48 MOHM SMD</t>
   </si>
   <si>
     <t>RED LED 0603 Light Emitting Diodes</t>
@@ -592,6 +654,9 @@
     <t>20V 2.2A 800mW 110mΩ@4.5V,2.7A 810mV@250uA P Channel SOT-23 MOSFETs ROHS</t>
   </si>
   <si>
+    <t>50V 220mA 3.5Ω@10V,220mA 225mW 1.6V@1mA N Channel SOT-23 MOSFETs ROHS</t>
+  </si>
+  <si>
     <t>RES 5.1K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -601,13 +666,22 @@
     <t>RES 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
+    <t>RES 0 OHM JUMPER 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 4.7K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
     <t>RES 0 OHM JUMPER 1/10W 0603</t>
   </si>
   <si>
-    <t>60.4kΩ 50V 62.5mW Thick Film Resistors ±1% 0402 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
-    <t>62.5mW Thick Film Resistors 50V ±100ppm/℃ ±1% 25.5kΩ 0402 Chip Resistor - Surface Mount ROHS</t>
+    <t>RES 33 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 158K OHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES SMD 30.1KOHM 0.1% 1/16W 0402</t>
   </si>
   <si>
     <t>RES 3.9K OHM 1% 1/16W 0402</t>
@@ -616,6 +690,9 @@
     <t>RES 470 OHM 1% 1/16W 0402</t>
   </si>
   <si>
+    <t>RES 200 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
     <t>RES 33K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -625,7 +702,22 @@
     <t>RES 100K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES 4.7K OHM 1% 1/16W 0402</t>
+    <t>RES SMD 1K OHM 1% 1/5W 0402</t>
+  </si>
+  <si>
+    <t>RES 49.9 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES SMD 10 OHM 1% 1/5W 0402</t>
+  </si>
+  <si>
+    <t>SMD Chip Resistor, 330 Ohm, ± 1%, 63 mW, 0402 [1005 Metric], Thick Film, General Purpose</t>
+  </si>
+  <si>
+    <t>RES SMD 12.4K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 2.2 OHM 1% 1/10W 0603</t>
   </si>
   <si>
     <t>RES 22 OHM 1% 1/20W 0201</t>
@@ -634,43 +726,19 @@
     <t>RES 120 OHM 5% 1/10W 0603</t>
   </si>
   <si>
+    <t>RESISTOR 0402 JUMPER ZERO OHM</t>
+  </si>
+  <si>
+    <t>RES  SMD 330R 100 mW 0603</t>
+  </si>
+  <si>
     <t>RES SMD 12.1KOHM 0.1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES  SMD 330R 100 mW 0603</t>
-  </si>
-  <si>
-    <t>RES 49.9 OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RESISTOR 0402 JUMPER ZERO OHM</t>
-  </si>
-  <si>
-    <t>RES 200 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 33 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES SMD 1K OHM 1% 1/5W 0402</t>
-  </si>
-  <si>
-    <t>RES SMD 10 OHM 1% 1/5W 0402</t>
-  </si>
-  <si>
-    <t>SMD Chip Resistor, 330 Ohm, ± 1%, 63 mW, 0402 [1005 Metric], Thick Film, General Purpose</t>
-  </si>
-  <si>
-    <t>RES SMD 12.4K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>62.5mW Thick Film Resistors 50V ±100ppm/℃ ±1% 1.05kΩ 0402 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
-    <t>RES SMD 137K OHM 0.1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>11.5kΩ 50V 62.5mW Thick Film Resistors ±100ppm/℃ ±1%  0402 Chip Resistor - Surface Mount ROHS</t>
+    <t>RES SMD 10K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
+    <t>RES SMD 220 OHM 1% 1/10W 0603</t>
   </si>
   <si>
     <t>RES ARRAY 4 RES 10K OHM 1206</t>
@@ -682,40 +750,52 @@
     <t>Tactile Switches SMT Top Push 0.9mm 7N Trav 100m Yellow</t>
   </si>
   <si>
+    <t>3 positions SPST Black Flat Toggle, Raised Style SMD-6P,6x7.6mm DIP Switches ROHS</t>
+  </si>
+  <si>
     <t>SMD MODULE, ESP32-S3R8 WITH 3.3V</t>
   </si>
   <si>
     <t>IC MCU 32BIT 512KB FLASH 64LQFP</t>
   </si>
   <si>
-    <t>IC REG BCK SPLIT RAIL ADJ 8SOPWR</t>
-  </si>
-  <si>
-    <t>72dB@(120Hz) 5A Fixed 3.3V~3.3V Positive 12V TO-263-3 Linear Voltage Regulators (LDO) ROHS</t>
+    <t>IC XPNDR 100KHZ I2C 20TSSOP</t>
+  </si>
+  <si>
+    <t>IC ADC 16BIT SIGMA-DELTA 10VSSOP</t>
+  </si>
+  <si>
+    <t>400kHz SO-8 I/O Expanders ROHS</t>
+  </si>
+  <si>
+    <t>IC REG BUCK ADJ 3A TSOT26</t>
+  </si>
+  <si>
+    <t>70dB@(100Hz) 1.5A Fixed 3.3V~3.3V Positive 6V SOT-223 Linear Voltage Regulators (LDO) ROHS</t>
   </si>
   <si>
     <t>IC TRANSCEIVER HALF 1/1 14VSON</t>
   </si>
   <si>
-    <t>SOT23-6 LED Drivers ROHS</t>
+    <t>SPI LQFP-48(7x7) Ethernet ICs ROHS</t>
+  </si>
+  <si>
+    <t>TVS DIODE 5.5VWM 8.5VC SOT23-5</t>
+  </si>
+  <si>
+    <t>IC TRANSLTR BIDIRECTIONAL 8VSSOP</t>
+  </si>
+  <si>
+    <t>250Kbps transceiver 2/2 SOP-16 RS232 ICs ROHS</t>
   </si>
   <si>
     <t>IC TRANSCEIVER HALF 1/1 8SON</t>
   </si>
   <si>
-    <t>250Kbps transceiver 2/2 SOP-16 RS232 ICs ROHS</t>
-  </si>
-  <si>
     <t>2/3-PORT ETHERCAT SLAVE CTLR</t>
   </si>
   <si>
-    <t>SPI LQFP-48(7x7) Ethernet ICs ROHS</t>
-  </si>
-  <si>
-    <t>TVS DIODE 5.5VWM 8.5VC SOT23-5</t>
-  </si>
-  <si>
-    <t>IC TRANSLTR BIDIRECTIONAL 8VSSOP</t>
+    <t>IC EEPROM 256KBIT I2C 1MHZ 8SOIC</t>
   </si>
   <si>
     <t>32.768kHz 12.5pF ±20ppm MC-306 Crystals ROHS</t>
@@ -736,90 +816,96 @@
     <t>Cap-0603</t>
   </si>
   <si>
+    <t>Cap-0402</t>
+  </si>
+  <si>
+    <t>cap-0402</t>
+  </si>
+  <si>
+    <t>UCD-220uF-10mmDia</t>
+  </si>
+  <si>
+    <t>Cap-1206</t>
+  </si>
+  <si>
     <t>Cap-0805</t>
   </si>
   <si>
-    <t>Cap-0402</t>
-  </si>
-  <si>
-    <t>cap-0402</t>
-  </si>
-  <si>
-    <t>RVT1A101M0605</t>
-  </si>
-  <si>
-    <t>UCD-220uF-10mmDia</t>
-  </si>
-  <si>
     <t>SOD-923.</t>
   </si>
   <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
     <t>SMB_</t>
   </si>
   <si>
     <t>DSN0603-2</t>
   </si>
   <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
     <t>SMB Bi Directional</t>
   </si>
   <si>
-    <t>SMA</t>
+    <t>Fuse-1812_</t>
   </si>
   <si>
     <t>Fuse-0805</t>
   </si>
   <si>
+    <t>IND-0603 (1608 Metric)</t>
+  </si>
+  <si>
+    <t>Ind-0805</t>
+  </si>
+  <si>
+    <t>HC-XH-2A-G</t>
+  </si>
+  <si>
+    <t>HDR 1X9 male</t>
+  </si>
+  <si>
+    <t>HDR1X3_</t>
+  </si>
+  <si>
+    <t>HDR1X5_</t>
+  </si>
+  <si>
+    <t>HDR1X4_</t>
+  </si>
+  <si>
+    <t>178.6165.0002</t>
+  </si>
+  <si>
+    <t>HDR1X2_</t>
+  </si>
+  <si>
+    <t>X12ADIWA3DY1027</t>
+  </si>
+  <si>
+    <t>HR911105A</t>
+  </si>
+  <si>
+    <t>AFC07-S32ECA-00</t>
+  </si>
+  <si>
+    <t>DB128L-5.08-3P-BK-S</t>
+  </si>
+  <si>
+    <t>T44001</t>
+  </si>
+  <si>
     <t>IND-0402</t>
   </si>
   <si>
-    <t>Ind-0805</t>
-  </si>
-  <si>
-    <t>HC-XH-2A-G</t>
-  </si>
-  <si>
-    <t>HDR1X4_</t>
-  </si>
-  <si>
-    <t>HDR1X3_</t>
-  </si>
-  <si>
-    <t>HDR1X6_</t>
-  </si>
-  <si>
-    <t>HDR 1x12 TH</t>
-  </si>
-  <si>
-    <t>HC-FPC-03-09-45RLTAG</t>
-  </si>
-  <si>
-    <t>WAFER-PH2.0-4PWB</t>
-  </si>
-  <si>
-    <t>T44001</t>
-  </si>
-  <si>
-    <t>HR911105A</t>
-  </si>
-  <si>
-    <t>MXHB9500-9.5-02P-BK01-Cu-S-A</t>
-  </si>
-  <si>
-    <t>WJ500V-5.08-3P</t>
-  </si>
-  <si>
-    <t>YSPI1050-4R7M</t>
-  </si>
-  <si>
-    <t>FXL0530-150-M</t>
-  </si>
-  <si>
     <t>LED-0603</t>
   </si>
   <si>
-    <t>SOT-23</t>
-  </si>
-  <si>
     <t>Sot-23</t>
   </si>
   <si>
@@ -838,40 +924,52 @@
     <t>B3U-1000P</t>
   </si>
   <si>
+    <t>DSIC03LSGET</t>
+  </si>
+  <si>
     <t>41-SMD Module</t>
   </si>
   <si>
     <t>LQFP-64(10x10)</t>
   </si>
   <si>
-    <t>8-SO PowerPad</t>
-  </si>
-  <si>
-    <t>TO263-3_</t>
+    <t>TSSOP-20</t>
+  </si>
+  <si>
+    <t>VSSOP-10</t>
+  </si>
+  <si>
+    <t>SOP-8</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>SOT- 223</t>
   </si>
   <si>
     <t>VSON-14(3x4.5)</t>
   </si>
   <si>
-    <t>SOT23-6</t>
+    <t>48-LQFP (7x7)_</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>VSSOP-8(3.1x2.1)</t>
+  </si>
+  <si>
+    <t>SO-Narrow-16</t>
   </si>
   <si>
     <t>SON-8-EP(3x3)</t>
   </si>
   <si>
-    <t>SOP-16</t>
-  </si>
-  <si>
     <t>QFN-64-EP(9x9)</t>
   </si>
   <si>
-    <t>48-LQFP (7x7)_</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
-    <t>VSSOP-8(3.1x2.1)</t>
+    <t>CAT24C256WI-GT3</t>
   </si>
   <si>
     <t>MC-306</t>
@@ -889,25 +987,40 @@
     <t>CC0603JRNPO9BN472</t>
   </si>
   <si>
-    <t>GRM21BR61H475KE51L</t>
+    <t>CC0603KRX5R7BB106</t>
   </si>
   <si>
     <t>CC0402JRX7R7BB104</t>
   </si>
   <si>
+    <t>CC0402CRNPO9BN6R8</t>
+  </si>
+  <si>
+    <t>CC0402GRNPO9BN300</t>
+  </si>
+  <si>
     <t>CC0402KRX5R6BB475</t>
   </si>
   <si>
     <t>C1005X7R1H104KT000F</t>
   </si>
   <si>
-    <t>CC0402CRNPO9BN6R8</t>
-  </si>
-  <si>
-    <t>CC0402JRNPO9BN200</t>
-  </si>
-  <si>
-    <t>C1608X5R1E106M080AC</t>
+    <t>C1005X5R1H104K050BB</t>
+  </si>
+  <si>
+    <t>GCM1555C1H470FA16D</t>
+  </si>
+  <si>
+    <t>UCD1H221MNL1GS</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R7BB475</t>
+  </si>
+  <si>
+    <t>CC1206KKX5R9BB106</t>
+  </si>
+  <si>
+    <t>CC0805MKX5R8BB226</t>
   </si>
   <si>
     <t>CC0402KRX7R9BB472</t>
@@ -916,73 +1029,70 @@
     <t>GRM155R62A104KE14D</t>
   </si>
   <si>
-    <t>C1005X5R1H104K050BB</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R6BB105</t>
-  </si>
-  <si>
-    <t>0603B471K500CT</t>
-  </si>
-  <si>
-    <t>GCM1555C1H180GA16D</t>
+    <t>CC0402KRX5R7BB105</t>
+  </si>
+  <si>
+    <t>GRM155R11H471KA01D</t>
   </si>
   <si>
     <t>GRM1555C1H100JA01D</t>
   </si>
   <si>
+    <t>C2012X5R1V226MT000E</t>
+  </si>
+  <si>
+    <t>0603B682K500NT</t>
+  </si>
+  <si>
+    <t>CC0603JRNPO9BN103</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB223</t>
+  </si>
+  <si>
+    <t>CC0603J*NPO9B*120</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R6BB475</t>
+  </si>
+  <si>
     <t>CC0402JRX7R7BB223</t>
   </si>
   <si>
-    <t>UCD1H221MNL1GS</t>
-  </si>
-  <si>
-    <t>C2012X5R1V226MT000E</t>
-  </si>
-  <si>
-    <t>CC0805MKX5R8BB226</t>
-  </si>
-  <si>
-    <t>CC0603KRX5R7BB106</t>
-  </si>
-  <si>
-    <t>0603B682K500NT</t>
-  </si>
-  <si>
-    <t>CC0603JRNPO9BN103</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB223</t>
-  </si>
-  <si>
-    <t>CC0603J*NPO9B*120</t>
-  </si>
-  <si>
-    <t>CC0603KRX5R6BB475</t>
-  </si>
-  <si>
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>MM3Z3V3</t>
+  </si>
+  <si>
+    <t>SS56</t>
+  </si>
+  <si>
     <t>SMBJ28A-13-F</t>
   </si>
   <si>
     <t>PESD5V0H1BSFYL</t>
   </si>
   <si>
-    <t>SMBJ26CA</t>
-  </si>
-  <si>
-    <t>SS56</t>
-  </si>
-  <si>
-    <t>SS24A</t>
+    <t>CDSOT23-T24CAN-Q</t>
+  </si>
+  <si>
+    <t>SM712</t>
+  </si>
+  <si>
+    <t>SMBJ8.0CA</t>
+  </si>
+  <si>
+    <t>MF-MSMF010-2</t>
   </si>
   <si>
     <t>SMD0805P020TF</t>
   </si>
   <si>
-    <t>BLM15PG100SN1D</t>
+    <t>BLM18PG221SN1D</t>
   </si>
   <si>
     <t>YI201209U301-2R0T</t>
@@ -994,18 +1104,30 @@
     <t>C145963</t>
   </si>
   <si>
+    <t>X6511WV-09H-C60D30</t>
+  </si>
+  <si>
+    <t>X6511WV-05H-C60D30</t>
+  </si>
+  <si>
     <t>X6511WV-04H-C60D30</t>
   </si>
   <si>
-    <t>X6511WV-06H-C60D30</t>
-  </si>
-  <si>
-    <t>X6511WV-12H-C60D30</t>
+    <t>B3B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>X6511WV-02H-C60D30</t>
+  </si>
+  <si>
+    <t>B4B-XH-A(LF)(SN)</t>
   </si>
   <si>
     <t>BLM15AG601SN1D</t>
   </si>
   <si>
+    <t>0630CDMCCDS-6R8MC</t>
+  </si>
+  <si>
     <t>NCD0603R3</t>
   </si>
   <si>
@@ -1018,6 +1140,9 @@
     <t>WPM2015-3/TR</t>
   </si>
   <si>
+    <t>BSS138</t>
+  </si>
+  <si>
     <t>RC0402FR-075K1L</t>
   </si>
   <si>
@@ -1027,13 +1152,22 @@
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
+    <t>RC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-074K7L</t>
+  </si>
+  <si>
     <t>RC0603JR-070RL</t>
   </si>
   <si>
-    <t>SCR0402F60K4</t>
-  </si>
-  <si>
-    <t>0402WGF2552TCE</t>
+    <t>RC0402FR-0733RL</t>
+  </si>
+  <si>
+    <t>RT0402BRE07158KL</t>
+  </si>
+  <si>
+    <t>RT0402BRD0730K1L</t>
   </si>
   <si>
     <t>RC0402FR-073K9L</t>
@@ -1042,6 +1176,9 @@
     <t>RC0402FR-07470RL</t>
   </si>
   <si>
+    <t>RC0402FR-07200RL</t>
+  </si>
+  <si>
     <t>RC0402FR-0733KL</t>
   </si>
   <si>
@@ -1051,7 +1188,22 @@
     <t>RC0402FR-07100KL</t>
   </si>
   <si>
-    <t>RC0402FR-074K7L</t>
+    <t>CRCW04021K00FKEDHP</t>
+  </si>
+  <si>
+    <t>RC0603FR-0749R9L</t>
+  </si>
+  <si>
+    <t>CRCW040210R0FKEDHP</t>
+  </si>
+  <si>
+    <t>CRCW0402330RFKEDC</t>
+  </si>
+  <si>
+    <t>RC0603FR-0712K4L</t>
+  </si>
+  <si>
+    <t>RC0603FR-072R2L</t>
   </si>
   <si>
     <t>RC0201FR-0722RL</t>
@@ -1060,43 +1212,19 @@
     <t>RC0603JR-07120RL</t>
   </si>
   <si>
+    <t>AC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>RC0603JR-07330RL</t>
+  </si>
+  <si>
     <t>RT0402BRD0712K1L</t>
   </si>
   <si>
-    <t>RC0603JR-07330RL</t>
-  </si>
-  <si>
-    <t>RC0603FR-0749R9L</t>
-  </si>
-  <si>
-    <t>AC0402FR-070RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-07200RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-0733RL</t>
-  </si>
-  <si>
-    <t>CRCW04021K00FKEDHP</t>
-  </si>
-  <si>
-    <t>CRCW040210R0FKEDHP</t>
-  </si>
-  <si>
-    <t>CRCW0402330RFKEDC</t>
-  </si>
-  <si>
-    <t>RC0603FR-0712K4L</t>
-  </si>
-  <si>
-    <t>0402WGF1051TCE</t>
-  </si>
-  <si>
-    <t>RT0402BRD07137KL</t>
-  </si>
-  <si>
-    <t>FRC0402F1152TS</t>
+    <t>RC0201FR-0710KL</t>
+  </si>
+  <si>
+    <t>RC0603FR-07220RL</t>
   </si>
   <si>
     <t>SKSTACE010</t>
@@ -1108,36 +1236,42 @@
     <t>STM32G0B1RET6</t>
   </si>
   <si>
-    <t>TPS54560BQDDARQ1</t>
-  </si>
-  <si>
-    <t>LM1084S-3.3/TR</t>
+    <t>PCF8574APWR</t>
+  </si>
+  <si>
+    <t>ADS1115IDGSR</t>
+  </si>
+  <si>
+    <t>PCA9536D,118</t>
+  </si>
+  <si>
+    <t>AP63300WU-7</t>
+  </si>
+  <si>
+    <t>BL8071CLATR33</t>
   </si>
   <si>
     <t>TCAN1463DMTRQ1</t>
   </si>
   <si>
-    <t>ETA1617S2G</t>
+    <t>W5500</t>
+  </si>
+  <si>
+    <t>SP0504BAHTG</t>
+  </si>
+  <si>
+    <t>TXB0102DCUR</t>
+  </si>
+  <si>
+    <t>MAX3232ESE</t>
   </si>
   <si>
     <t>THVD2450DRBR</t>
   </si>
   <si>
-    <t>MAX3232ESE</t>
-  </si>
-  <si>
     <t>LAN9253-I/R4X</t>
   </si>
   <si>
-    <t>W5500</t>
-  </si>
-  <si>
-    <t>SP0504BAHTG</t>
-  </si>
-  <si>
-    <t>TXB0102DCUR</t>
-  </si>
-  <si>
     <t>MC-306 32.7680K-A0:ROHS</t>
   </si>
   <si>
@@ -1153,21 +1287,18 @@
     <t>Yageo</t>
   </si>
   <si>
+    <t>TDK</t>
+  </si>
+  <si>
     <t>Murata</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>ROQANG</t>
-  </si>
-  <si>
-    <t>Walsin Technologies</t>
-  </si>
-  <si>
     <t>Nichicon</t>
   </si>
   <si>
+    <t>Murata Electronics</t>
+  </si>
+  <si>
     <t>TDK Corporation</t>
   </si>
   <si>
@@ -1177,19 +1308,25 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>JSMSEMI</t>
+  </si>
+  <si>
     <t>Diodes</t>
   </si>
   <si>
     <t>Nexperia</t>
   </si>
   <si>
-    <t>MSKSEMI</t>
-  </si>
-  <si>
-    <t>MDD</t>
-  </si>
-  <si>
-    <t>Guangdong Hottech</t>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
   </si>
   <si>
     <t>RUILON</t>
@@ -1210,22 +1347,31 @@
     <t>XKB</t>
   </si>
   <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>Littelfuse Wickmann</t>
+  </si>
+  <si>
     <t>Phoenix Contact</t>
   </si>
   <si>
+    <t>XKB Connection</t>
+  </si>
+  <si>
+    <t>HANRUN</t>
+  </si>
+  <si>
+    <t>JUSHUO</t>
+  </si>
+  <si>
+    <t>DIBO</t>
+  </si>
+  <si>
     <t>XFCN</t>
   </si>
   <si>
-    <t>HANRUN</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>Ningbo Kangnex Elec</t>
-  </si>
-  <si>
-    <t>cjiang</t>
+    <t>Sumida</t>
   </si>
   <si>
     <t>Foshan NationStar Optoelectronics</t>
@@ -1237,10 +1383,7 @@
     <t>WILLSEMI</t>
   </si>
   <si>
-    <t>VO</t>
-  </si>
-  <si>
-    <t>Royal Electronic Factory</t>
+    <t>Slkor(SLKORMICRO Elec.)</t>
   </si>
   <si>
     <t>YAGEO</t>
@@ -1252,18 +1395,15 @@
     <t>Vishay Semiconductors</t>
   </si>
   <si>
-    <t>UNI-Royal</t>
-  </si>
-  <si>
-    <t>FOJAN</t>
-  </si>
-  <si>
     <t>Omron</t>
   </si>
   <si>
     <t>Alps Electric</t>
   </si>
   <si>
+    <t>DongGuan KINGTEK Industrial Co.,LTD</t>
+  </si>
+  <si>
     <t>Espressif Systems</t>
   </si>
   <si>
@@ -1273,10 +1413,13 @@
     <t>Texas Instruments</t>
   </si>
   <si>
-    <t>HGSEMI</t>
-  </si>
-  <si>
-    <t>etasolutions</t>
+    <t>NXP Semiconductors</t>
+  </si>
+  <si>
+    <t>BL(Shanghai Belling)</t>
+  </si>
+  <si>
+    <t>WIZNET</t>
   </si>
   <si>
     <t>UMW</t>
@@ -1285,12 +1428,6 @@
     <t>Microchip</t>
   </si>
   <si>
-    <t>WIZNET</t>
-  </si>
-  <si>
-    <t>Littelfuse</t>
-  </si>
-  <si>
     <t>Seiko Epson</t>
   </si>
   <si>
@@ -1303,31 +1440,31 @@
     <t>4.7nF</t>
   </si>
   <si>
-    <t>4.7uf</t>
+    <t>10uF</t>
   </si>
   <si>
     <t>0.1uF</t>
   </si>
   <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>30pF</t>
+  </si>
+  <si>
     <t>4.7uF</t>
   </si>
   <si>
     <t>100nF</t>
   </si>
   <si>
-    <t>DNP</t>
-  </si>
-  <si>
-    <t>20pF</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>6.8pF</t>
+    <t>47pF</t>
+  </si>
+  <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>22uF</t>
   </si>
   <si>
     <t>0.1uf</t>
@@ -1339,34 +1476,28 @@
     <t>470pF</t>
   </si>
   <si>
-    <t>18pF</t>
+    <t>10pF</t>
+  </si>
+  <si>
+    <t>6.8nF</t>
+  </si>
+  <si>
+    <t>10nF</t>
   </si>
   <si>
     <t>22nF</t>
   </si>
   <si>
-    <t>220uF</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>6.8nF</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
     <t>12pF</t>
   </si>
   <si>
     <t>100MHz</t>
   </si>
   <si>
-    <t>4.7uH</t>
-  </si>
-  <si>
-    <t>15uH</t>
+    <t>68000-103HLF</t>
+  </si>
+  <si>
+    <t>6.8uH</t>
   </si>
   <si>
     <t>5.1K</t>
@@ -1378,13 +1509,19 @@
     <t>10K</t>
   </si>
   <si>
+    <t>4.7K</t>
+  </si>
+  <si>
     <t>0R</t>
   </si>
   <si>
-    <t>60.4K</t>
-  </si>
-  <si>
-    <t>25.5K</t>
+    <t>33R</t>
+  </si>
+  <si>
+    <t>158K</t>
+  </si>
+  <si>
+    <t>30.1K</t>
   </si>
   <si>
     <t>3.9K</t>
@@ -1393,6 +1530,9 @@
     <t>470R</t>
   </si>
   <si>
+    <t>200R</t>
+  </si>
+  <si>
     <t>33K</t>
   </si>
   <si>
@@ -1402,7 +1542,22 @@
     <t>100K</t>
   </si>
   <si>
-    <t>4.7K</t>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>49.9R</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>330R</t>
+  </si>
+  <si>
+    <t>12.4K</t>
+  </si>
+  <si>
+    <t>2.2R</t>
   </si>
   <si>
     <t>22R</t>
@@ -1414,34 +1569,7 @@
     <t>12.1k</t>
   </si>
   <si>
-    <t>330R</t>
-  </si>
-  <si>
-    <t>49.9R</t>
-  </si>
-  <si>
-    <t>200R</t>
-  </si>
-  <si>
-    <t>33R</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>12.4K</t>
-  </si>
-  <si>
-    <t>1.05K</t>
-  </si>
-  <si>
-    <t>137K</t>
-  </si>
-  <si>
-    <t>11.5K</t>
+    <t>220R</t>
   </si>
   <si>
     <t>8MHz</t>
@@ -1453,41 +1581,41 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Amphenol</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
     <t>Custom</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Remarks</t>
+    <t>DO NOT PLACE</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>DO NOT PLACE</t>
-  </si>
-  <si>
-    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
-  </si>
-  <si>
-    <t>SOD-323</t>
-  </si>
-  <si>
-    <t>SD03</t>
-  </si>
-  <si>
-    <t>68000-103HLF</t>
-  </si>
-  <si>
-    <t>Amphenol</t>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>3.5" inch 320*480 32P/0.5 ST7796 8/16 MCU Parallel 3/4 SPI TFT Color LCD Module Display Screen Resistive Capacitive Touch Panel</t>
+  </si>
+  <si>
+    <t>CN-TN-ST7796-NTP</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1543,6 +1671,14 @@
       <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1660,10 +1796,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1709,6 +1846,12 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1718,8 +1861,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2005,19 +2155,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2029,9 +2179,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2042,28 +2192,28 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>375</v>
+        <v>420</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>478</v>
+        <v>521</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2076,22 +2226,22 @@
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>426</v>
+        <v>472</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
@@ -2101,36 +2251,36 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B108" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B119" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>427</v>
+        <v>473</v>
       </c>
       <c r="J4" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -2140,61 +2290,63 @@
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="J5" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="J6" s="9">
+      <c r="D6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="J6" s="14">
         <v>2</v>
       </c>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="16" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -2204,30 +2356,30 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>430</v>
+        <v>476</v>
       </c>
       <c r="J7" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2235,32 +2387,30 @@
       <c r="C8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="J8" s="14">
-        <v>2</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -2270,57 +2420,57 @@
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>432</v>
+        <v>478</v>
       </c>
       <c r="J9" s="7">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>477</v>
+        <v>265</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>379</v>
+        <v>422</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="J10" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K10" s="9"/>
     </row>
@@ -2330,29 +2480,29 @@
         <f>ROW(B11) - ROW($B$2)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="J11" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="7"/>
     </row>
@@ -2366,25 +2516,25 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
       <c r="J12" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="9"/>
     </row>
@@ -2398,25 +2548,25 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>426</v>
+        <v>477</v>
       </c>
       <c r="J13" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="7"/>
     </row>
@@ -2427,28 +2577,28 @@
         <v>12</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="J14" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K14" s="9"/>
     </row>
@@ -2462,25 +2612,25 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>428</v>
+        <v>481</v>
       </c>
       <c r="J15" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K15" s="7"/>
     </row>
@@ -2494,25 +2644,25 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="J16" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" s="9"/>
     </row>
@@ -2526,25 +2676,25 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>380</v>
+        <v>423</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="J17" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K17" s="7"/>
     </row>
@@ -2558,29 +2708,29 @@
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>439</v>
+        <v>483</v>
       </c>
       <c r="J18" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -2589,30 +2739,28 @@
       <c r="C19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="J19" s="14">
-        <v>8</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>481</v>
-      </c>
+      <c r="D19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="J19" s="7">
+        <v>1</v>
+      </c>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2624,25 +2772,25 @@
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>376</v>
+        <v>423</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>440</v>
+        <v>485</v>
       </c>
       <c r="J20" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K20" s="9"/>
     </row>
@@ -2656,25 +2804,25 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>381</v>
+        <v>426</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="J21" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" s="7"/>
     </row>
@@ -2688,25 +2836,25 @@
         <v>2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>382</v>
+        <v>427</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="J22" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="9"/>
     </row>
@@ -2720,25 +2868,25 @@
         <v>2</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>442</v>
+        <v>487</v>
       </c>
       <c r="J23" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="7"/>
     </row>
@@ -2752,25 +2900,25 @@
         <v>2</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>307</v>
+        <v>342</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>434</v>
+        <v>488</v>
       </c>
       <c r="J24" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" s="9"/>
     </row>
@@ -2784,22 +2932,22 @@
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
@@ -2816,25 +2964,25 @@
         <v>2</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="J26" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="9"/>
     </row>
@@ -2848,25 +2996,25 @@
         <v>2</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="J27" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="7"/>
     </row>
@@ -2877,124 +3025,124 @@
         <v>26</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>376</v>
+        <v>428</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>445</v>
+        <v>525</v>
       </c>
       <c r="J28" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J29" s="7">
         <v>2</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="J29" s="7">
-        <v>1</v>
-      </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>3</v>
+      <c r="C30" s="13" t="s">
+        <v>5</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J30" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>3</v>
+      <c r="C31" s="13" t="s">
+        <v>5</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>388</v>
+        <v>61</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>429</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J31" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -3005,25 +3153,25 @@
         <v>30</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -3037,28 +3185,28 @@
         <v>31</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J33" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -3069,28 +3217,28 @@
         <v>32</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J34" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K34" s="9"/>
     </row>
@@ -3100,61 +3248,61 @@
         <f>ROW(B35) - ROW($B$2)</f>
         <v>33</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J35" s="7">
         <v>3</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="J35" s="7">
-        <v>1</v>
-      </c>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J36" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K36" s="9"/>
     </row>
@@ -3165,92 +3313,92 @@
         <v>35</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J37" s="7">
         <v>8</v>
       </c>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>377</v>
+        <v>436</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J38" s="9">
         <v>2</v>
       </c>
       <c r="K38" s="9"/>
     </row>
-    <row r="39" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
         <v>37</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>446</v>
+        <v>423</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>525</v>
       </c>
       <c r="J39" s="7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K39" s="7"/>
     </row>
@@ -3261,350 +3409,352 @@
         <v>38</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>477</v>
+        <v>280</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>392</v>
+        <v>437</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="J40" s="9">
         <v>2</v>
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>477</v>
+        <v>188</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>251</v>
+        <v>359</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>480</v>
+        <v>438</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J41" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>477</v>
+        <v>189</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>480</v>
+        <v>439</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J42" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f>ROW(B43) - ROW($B$2)</f>
         <v>41</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>252</v>
+        <v>523</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>480</v>
+        <v>440</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J43" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>480</v>
+        <v>282</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
       </c>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f>ROW(B45) - ROW($B$2)</f>
         <v>43</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>325</v>
+        <v>491</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>480</v>
+        <v>520</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J45" s="7">
         <v>1</v>
       </c>
       <c r="K45" s="7"/>
     </row>
-    <row r="46" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>480</v>
+        <v>441</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J46" s="9">
         <v>1</v>
       </c>
       <c r="K46" s="9"/>
     </row>
-    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="G47" s="8">
-        <v>1715721</v>
+        <v>194</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>363</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>480</v>
+        <v>441</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J47" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>477</v>
+        <v>195</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>480</v>
+        <v>442</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J48" s="9">
         <v>1</v>
       </c>
       <c r="K48" s="9"/>
     </row>
-    <row r="49" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>477</v>
+        <v>196</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="10" t="s">
-        <v>480</v>
+        <v>286</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
       </c>
       <c r="K49" s="7"/>
     </row>
-    <row r="50" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>8</v>
+      <c r="C50" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>258</v>
+        <v>197</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G50" s="10">
+        <v>1715721</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>480</v>
+        <v>444</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J50" s="9">
         <v>1</v>
       </c>
       <c r="K50" s="9"/>
     </row>
-    <row r="51" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f>ROW(B51) - ROW($B$2)</f>
@@ -3614,25 +3764,25 @@
         <v>12</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>477</v>
+        <v>198</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>480</v>
+        <v>441</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J51" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K51" s="7"/>
     </row>
@@ -3643,156 +3793,156 @@
         <v>50</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>477</v>
+        <v>199</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>480</v>
+        <v>445</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J52" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="9"/>
     </row>
-    <row r="53" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>477</v>
+        <v>200</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>480</v>
+        <v>446</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J53" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>249</v>
+        <v>201</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>480</v>
+        <v>447</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J54" s="9">
         <v>1</v>
       </c>
       <c r="K54" s="9"/>
     </row>
-    <row r="55" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>477</v>
+        <v>202</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>447</v>
+        <v>525</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
       </c>
       <c r="K55" s="7"/>
     </row>
-    <row r="56" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>477</v>
+        <v>203</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="I56" s="10" t="s">
         <v>448</v>
       </c>
+      <c r="I56" s="8" t="s">
+        <v>525</v>
+      </c>
       <c r="J56" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K56" s="9"/>
     </row>
@@ -3802,257 +3952,253 @@
         <f>ROW(B57) - ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="C57" s="12"/>
       <c r="D57" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>264</v>
+        <v>523</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J57" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J58" s="9">
         <v>1</v>
       </c>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>265</v>
+        <v>523</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>403</v>
+        <v>450</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
       </c>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>480</v>
+        <v>451</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>525</v>
       </c>
       <c r="J60" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K60" s="9"/>
     </row>
-    <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f>ROW(B61) - ROW($B$2)</f>
         <v>59</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>525</v>
       </c>
       <c r="J61" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K61" s="7"/>
     </row>
-    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>376</v>
+        <v>452</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="J62" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K62" s="9"/>
     </row>
-    <row r="63" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f>ROW(B63) - ROW($B$2)</f>
         <v>61</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>525</v>
       </c>
       <c r="J63" s="7">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K63" s="7"/>
     </row>
-    <row r="64" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="G64" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="H64" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="J64" s="14">
-        <v>2</v>
-      </c>
-      <c r="K64" s="16" t="s">
-        <v>481</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="J64" s="9">
+        <v>1</v>
+      </c>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
@@ -4061,282 +4207,288 @@
         <v>63</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="J65" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="J66" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f>ROW(B67) - ROW($B$2)</f>
         <v>65</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="J67" s="7">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
+    <row r="68" spans="1:11" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="19"/>
       <c r="B68" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="I68" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="J68" s="9">
-        <v>1</v>
-      </c>
-      <c r="K68" s="9"/>
-    </row>
-    <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="J68" s="14">
+        <v>2</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f>ROW(B69) - ROW($B$2)</f>
         <v>67</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>456</v>
+        <v>496</v>
       </c>
       <c r="J69" s="7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
+    <row r="70" spans="1:11" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="19"/>
       <c r="B70" s="11">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="J70" s="9">
-        <v>1</v>
-      </c>
-      <c r="K70" s="9"/>
-    </row>
-    <row r="71" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="J70" s="14">
+        <v>2</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f>ROW(B71) - ROW($B$2)</f>
         <v>69</v>
       </c>
-      <c r="C71" s="13" t="s">
-        <v>17</v>
+      <c r="C71" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="H71" s="7"/>
+        <v>379</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>421</v>
+      </c>
       <c r="I71" s="8" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="J71" s="7">
         <v>2</v>
       </c>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>17</v>
+      <c r="C72" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="J72" s="9">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K72" s="9"/>
     </row>
-    <row r="73" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f>ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="J73" s="7">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K73" s="7"/>
     </row>
@@ -4347,28 +4499,28 @@
         <v>72</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="J74" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K74" s="9"/>
     </row>
@@ -4379,28 +4531,28 @@
         <v>73</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="J75" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K75" s="7"/>
     </row>
@@ -4411,25 +4563,25 @@
         <v>74</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
@@ -4443,32 +4595,30 @@
         <v>75</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="G77" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="I77" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="J77" s="14">
+        <v>22</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="J77" s="7">
         <v>1</v>
       </c>
-      <c r="K77" s="16" t="s">
-        <v>481</v>
-      </c>
+      <c r="K77" s="7"/>
     </row>
     <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -4476,93 +4626,91 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>17</v>
+      <c r="C78" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
       <c r="J78" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f>ROW(B79) - ROW($B$2)</f>
         <v>77</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>376</v>
+        <v>455</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="J79" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>17</v>
+      <c r="C80" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>376</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="H80" s="9"/>
       <c r="I80" s="10" t="s">
-        <v>452</v>
+        <v>505</v>
       </c>
       <c r="J80" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K80" s="9"/>
     </row>
@@ -4572,29 +4720,29 @@
         <f>ROW(B81) - ROW($B$2)</f>
         <v>79</v>
       </c>
-      <c r="C81" s="13" t="s">
-        <v>17</v>
+      <c r="C81" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>466</v>
+        <v>506</v>
       </c>
       <c r="J81" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="7"/>
     </row>
@@ -4604,61 +4752,61 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>17</v>
+      <c r="C82" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>376</v>
+        <v>456</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>467</v>
+        <v>507</v>
       </c>
       <c r="J82" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f>ROW(B83) - ROW($B$2)</f>
         <v>81</v>
       </c>
-      <c r="C83" s="13" t="s">
-        <v>17</v>
+      <c r="C83" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>468</v>
+        <v>508</v>
       </c>
       <c r="J83" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K83" s="7"/>
     </row>
@@ -4668,26 +4816,26 @@
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C84" s="13" t="s">
-        <v>17</v>
+      <c r="C84" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="J84" s="9">
         <v>1</v>
@@ -4700,26 +4848,26 @@
         <f>ROW(B85) - ROW($B$2)</f>
         <v>83</v>
       </c>
-      <c r="C85" s="13" t="s">
-        <v>17</v>
+      <c r="C85" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="J85" s="7">
         <v>2</v>
@@ -4733,124 +4881,124 @@
         <v>84</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="J86" s="9">
         <v>1</v>
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
         <f>ROW(B87) - ROW($B$2)</f>
         <v>85</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="J87" s="7">
         <v>1</v>
       </c>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="J88" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
         <f>ROW(B89) - ROW($B$2)</f>
         <v>87</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="J89" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K89" s="7"/>
     </row>
@@ -4861,28 +5009,28 @@
         <v>88</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>477</v>
+        <v>296</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>270</v>
+        <v>397</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="J90" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K90" s="9"/>
     </row>
@@ -4893,94 +5041,96 @@
         <v>89</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>477</v>
+        <v>236</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>297</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>271</v>
+        <v>398</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="J91" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K91" s="7"/>
     </row>
-    <row r="92" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>20</v>
+      <c r="C92" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>477</v>
+        <v>296</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="I92" s="8" t="s">
-        <v>480</v>
+        <v>421</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>515</v>
       </c>
       <c r="J92" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K92" s="9"/>
     </row>
-    <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
+    <row r="93" spans="1:11" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="19"/>
       <c r="B93" s="11">
         <f>ROW(B93) - ROW($B$2)</f>
         <v>91</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="I93" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="J93" s="7">
+        <v>22</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F93" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="H93" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="I93" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="J93" s="17">
         <v>1</v>
       </c>
-      <c r="K93" s="7"/>
+      <c r="K93" s="16" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -4992,22 +5142,22 @@
         <v>22</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="I94" s="8" t="s">
-        <v>480</v>
+        <v>421</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>495</v>
       </c>
       <c r="J94" s="9">
         <v>1</v>
@@ -5021,60 +5171,60 @@
         <v>93</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="J95" s="7">
         <v>1</v>
       </c>
       <c r="K95" s="7"/>
     </row>
-    <row r="96" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>275</v>
+        <v>523</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="I96" s="8" t="s">
-        <v>480</v>
+        <v>421</v>
+      </c>
+      <c r="I96" s="10" t="s">
+        <v>495</v>
       </c>
       <c r="J96" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K96" s="9"/>
     </row>
@@ -5085,121 +5235,121 @@
         <v>95</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>276</v>
+        <v>241</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>523</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>364</v>
+        <v>300</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>416</v>
+        <v>458</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J97" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K97" s="7"/>
     </row>
-    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C98" s="13" t="s">
-        <v>24</v>
+      <c r="C98" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>277</v>
+        <v>523</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J98" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f>ROW(B99) - ROW($B$2)</f>
         <v>97</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>278</v>
+        <v>243</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>523</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>366</v>
+        <v>301</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J99" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99" s="7"/>
     </row>
-    <row r="100" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J100" s="9">
         <v>1</v>
@@ -5213,25 +5363,25 @@
         <v>99</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J101" s="7">
         <v>1</v>
@@ -5245,25 +5395,25 @@
         <v>100</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J102" s="9">
         <v>1</v>
@@ -5276,26 +5426,26 @@
         <f>ROW(B103) - ROW($B$2)</f>
         <v>101</v>
       </c>
-      <c r="C103" s="13" t="s">
-        <v>23</v>
+      <c r="C103" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J103" s="7">
         <v>1</v>
@@ -5309,126 +5459,124 @@
         <v>102</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>416</v>
+        <v>464</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="J104" s="9">
         <v>1</v>
       </c>
       <c r="K104" s="9"/>
     </row>
-    <row r="105" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="11">
         <f>ROW(B105) - ROW($B$2)</f>
         <v>103</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E105" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="G105" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="I105" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="H105" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="J105" s="14">
+      <c r="I105" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J105" s="7">
         <v>1</v>
       </c>
-      <c r="K105" s="16" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K105" s="7"/>
+    </row>
+    <row r="106" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="11">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>477</v>
+        <v>308</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="I106" s="10" t="s">
-        <v>474</v>
+        <v>465</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J106" s="9">
         <v>1</v>
       </c>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
         <f>ROW(B107) - ROW($B$2)</f>
         <v>105</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>475</v>
+        <v>525</v>
       </c>
       <c r="J107" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K107" s="7"/>
     </row>
@@ -5439,36 +5587,394 @@
         <v>106</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>477</v>
+        <v>310</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>286</v>
+        <v>411</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="I108" s="10" t="s">
-        <v>475</v>
+        <v>466</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="J108" s="9">
         <v>1</v>
       </c>
       <c r="K108" s="9"/>
+    </row>
+    <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1"/>
+      <c r="B109" s="11">
+        <f>ROW(B109) - ROW($B$2)</f>
+        <v>107</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J109" s="7">
+        <v>1</v>
+      </c>
+      <c r="K109" s="7"/>
+    </row>
+    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1"/>
+      <c r="B110" s="11">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J110" s="9">
+        <v>1</v>
+      </c>
+      <c r="K110" s="9"/>
+    </row>
+    <row r="111" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1"/>
+      <c r="B111" s="11">
+        <f>ROW(B111) - ROW($B$2)</f>
+        <v>109</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J111" s="7">
+        <v>1</v>
+      </c>
+      <c r="K111" s="7"/>
+    </row>
+    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1"/>
+      <c r="B112" s="11">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J112" s="9">
+        <v>3</v>
+      </c>
+      <c r="K112" s="9"/>
+    </row>
+    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="B113" s="11">
+        <f>ROW(B113) - ROW($B$2)</f>
+        <v>111</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J113" s="7">
+        <v>1</v>
+      </c>
+      <c r="K113" s="7"/>
+    </row>
+    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1"/>
+      <c r="B114" s="11">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J114" s="9">
+        <v>1</v>
+      </c>
+      <c r="K114" s="9"/>
+    </row>
+    <row r="115" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1"/>
+      <c r="B115" s="11">
+        <f>ROW(B115) - ROW($B$2)</f>
+        <v>113</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="F115" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="G115" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="H115" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="I115" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="J115" s="14">
+        <v>1</v>
+      </c>
+      <c r="K115" s="16" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1"/>
+      <c r="B116" s="11">
+        <f t="shared" si="0"/>
+        <v>114</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="J116" s="9">
+        <v>1</v>
+      </c>
+      <c r="K116" s="9"/>
+    </row>
+    <row r="117" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1"/>
+      <c r="B117" s="11">
+        <f>ROW(B117) - ROW($B$2)</f>
+        <v>115</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="J117" s="7">
+        <v>1</v>
+      </c>
+      <c r="K117" s="7"/>
+    </row>
+    <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1"/>
+      <c r="B118" s="11">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="J118" s="9">
+        <v>1</v>
+      </c>
+      <c r="K118" s="9"/>
+    </row>
+    <row r="119" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B119" s="11">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="I119" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="J119" s="9">
+        <v>1</v>
+      </c>
+      <c r="K119" s="23" t="s">
+        <v>529</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K119" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="544">
   <si>
     <t>#</t>
   </si>
@@ -1609,6 +1609,48 @@
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGREEN </t>
+  </si>
+  <si>
+    <t>TFT Module</t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 2A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287002.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>SSD1315 I2C 128x64 0.96 OLED Display ROHS</t>
+  </si>
+  <si>
+    <t>HS96L03W2C03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS </t>
   </si>
 </sst>
 </file>
@@ -1858,14 +1900,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2155,7 +2197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2179,9 +2221,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2251,7 +2293,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B119" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B120" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -2312,7 +2354,7 @@
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -4200,7 +4242,7 @@
       </c>
       <c r="K64" s="9"/>
     </row>
-    <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f>ROW(B65) - ROW($B$2)</f>
@@ -4232,7 +4274,7 @@
       </c>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="0"/>
@@ -4264,7 +4306,7 @@
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f>ROW(B67) - ROW($B$2)</f>
@@ -4296,7 +4338,7 @@
       </c>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:11" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19"/>
       <c r="B68" s="11">
         <f t="shared" si="0"/>
@@ -4329,8 +4371,10 @@
       <c r="K68" s="16" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M68"/>
+      <c r="N68"/>
+    </row>
+    <row r="69" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f>ROW(B69) - ROW($B$2)</f>
@@ -4362,7 +4406,7 @@
       </c>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" spans="1:11" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19"/>
       <c r="B70" s="11">
         <f t="shared" si="0"/>
@@ -4395,8 +4439,10 @@
       <c r="K70" s="16" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M70"/>
+      <c r="N70"/>
+    </row>
+    <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f>ROW(B71) - ROW($B$2)</f>
@@ -4428,7 +4474,7 @@
       </c>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f t="shared" si="0"/>
@@ -4460,7 +4506,7 @@
       </c>
       <c r="K72" s="9"/>
     </row>
-    <row r="73" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f>ROW(B73) - ROW($B$2)</f>
@@ -4492,7 +4538,7 @@
       </c>
       <c r="K73" s="7"/>
     </row>
-    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f t="shared" si="0"/>
@@ -4524,7 +4570,7 @@
       </c>
       <c r="K74" s="9"/>
     </row>
-    <row r="75" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f>ROW(B75) - ROW($B$2)</f>
@@ -4556,7 +4602,7 @@
       </c>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f t="shared" si="0"/>
@@ -4588,7 +4634,7 @@
       </c>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f>ROW(B77) - ROW($B$2)</f>
@@ -4620,7 +4666,7 @@
       </c>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f t="shared" si="0"/>
@@ -4652,7 +4698,7 @@
       </c>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f>ROW(B79) - ROW($B$2)</f>
@@ -4684,7 +4730,7 @@
       </c>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="0"/>
@@ -4714,7 +4760,7 @@
       </c>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f>ROW(B81) - ROW($B$2)</f>
@@ -4746,7 +4792,7 @@
       </c>
       <c r="K81" s="7"/>
     </row>
-    <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f t="shared" si="0"/>
@@ -4778,7 +4824,7 @@
       </c>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f>ROW(B83) - ROW($B$2)</f>
@@ -4810,7 +4856,7 @@
       </c>
       <c r="K83" s="7"/>
     </row>
-    <row r="84" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f t="shared" si="0"/>
@@ -4842,7 +4888,7 @@
       </c>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f>ROW(B85) - ROW($B$2)</f>
@@ -4874,7 +4920,7 @@
       </c>
       <c r="K85" s="7"/>
     </row>
-    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="0"/>
@@ -4906,7 +4952,7 @@
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
         <f>ROW(B87) - ROW($B$2)</f>
@@ -4938,7 +4984,7 @@
       </c>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f t="shared" si="0"/>
@@ -4970,7 +5016,7 @@
       </c>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
         <f>ROW(B89) - ROW($B$2)</f>
@@ -5002,7 +5048,7 @@
       </c>
       <c r="K89" s="7"/>
     </row>
-    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f t="shared" si="0"/>
@@ -5034,7 +5080,7 @@
       </c>
       <c r="K90" s="9"/>
     </row>
-    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f>ROW(B91) - ROW($B$2)</f>
@@ -5066,7 +5112,7 @@
       </c>
       <c r="K91" s="7"/>
     </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f t="shared" si="0"/>
@@ -5098,7 +5144,7 @@
       </c>
       <c r="K92" s="9"/>
     </row>
-    <row r="93" spans="1:11" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="19"/>
       <c r="B93" s="11">
         <f>ROW(B93) - ROW($B$2)</f>
@@ -5131,8 +5177,10 @@
       <c r="K93" s="16" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M93"/>
+      <c r="N93"/>
+    </row>
+    <row r="94" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
         <f t="shared" si="0"/>
@@ -5164,7 +5212,7 @@
       </c>
       <c r="K94" s="9"/>
     </row>
-    <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
         <f>ROW(B95) - ROW($B$2)</f>
@@ -5196,7 +5244,7 @@
       </c>
       <c r="K95" s="7"/>
     </row>
-    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f t="shared" si="0"/>
@@ -5943,7 +5991,7 @@
         <v>526</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>527</v>
@@ -5957,15 +6005,147 @@
       <c r="H119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="I119" s="22" t="s">
+      <c r="I119" s="21" t="s">
         <v>525</v>
       </c>
       <c r="J119" s="9">
         <v>1</v>
       </c>
-      <c r="K119" s="23" t="s">
+      <c r="K119" s="22" t="s">
         <v>529</v>
       </c>
+    </row>
+    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="11">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="I120" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="J120" s="9">
+        <v>8</v>
+      </c>
+      <c r="K120" s="22"/>
+    </row>
+    <row r="121" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="11">
+        <f t="shared" ref="B121:B125" si="1">ROW(B121) - ROW($B$2)</f>
+        <v>119</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G121" s="8">
+        <v>50173</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I121" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="J121" s="9">
+        <v>2</v>
+      </c>
+      <c r="K121" s="22"/>
+    </row>
+    <row r="122" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="11">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I122" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="J122" s="9">
+        <v>1</v>
+      </c>
+      <c r="K122" s="22"/>
+    </row>
+    <row r="123" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="11">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="I123" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="J123" s="9">
+        <v>1</v>
+      </c>
+      <c r="K123" s="22"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B124"/>
+      <c r="C124"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B125"/>
+      <c r="C125"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
@@ -1605,9 +1605,6 @@
     <t>3.5" inch 320*480 32P/0.5 ST7796 8/16 MCU Parallel 3/4 SPI TFT Color LCD Module Display Screen Resistive Capacitive Touch Panel</t>
   </si>
   <si>
-    <t>CN-TN-ST7796-NTP</t>
-  </si>
-  <si>
     <t>Aliexpress</t>
   </si>
   <si>
@@ -1651,6 +1648,9 @@
   </si>
   <si>
     <t xml:space="preserve">HS </t>
+  </si>
+  <si>
+    <t>CS-IPS-ST7796-NTP</t>
   </si>
 </sst>
 </file>
@@ -5991,7 +5991,7 @@
         <v>526</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>527</v>
@@ -6000,7 +6000,7 @@
         <v>523</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="H119" s="9" t="s">
         <v>525</v>
@@ -6012,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="K119" s="22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6024,16 +6024,16 @@
         <v>526</v>
       </c>
       <c r="D120" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E120" s="8" t="s">
         <v>530</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>531</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>523</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>445</v>
@@ -6048,17 +6048,17 @@
     </row>
     <row r="121" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B121" s="11">
-        <f t="shared" ref="B121:B125" si="1">ROW(B121) - ROW($B$2)</f>
+        <f t="shared" ref="B121:B123" si="1">ROW(B121) - ROW($B$2)</f>
         <v>119</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>526</v>
       </c>
       <c r="D121" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="E121" s="8" t="s">
         <v>533</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>534</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>523</v>
@@ -6067,7 +6067,7 @@
         <v>50173</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I121" s="21" t="s">
         <v>525</v>
@@ -6089,16 +6089,16 @@
         <v>7</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>523</v>
       </c>
       <c r="G122" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="H122" s="9" t="s">
         <v>538</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>539</v>
       </c>
       <c r="I122" s="21" t="s">
         <v>525</v>
@@ -6117,19 +6117,19 @@
         <v>526</v>
       </c>
       <c r="D123" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="E123" s="9" t="s">
         <v>540</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>541</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>523</v>
       </c>
       <c r="G123" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="H123" s="9" t="s">
         <v>542</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>543</v>
       </c>
       <c r="I123" s="21" t="s">
         <v>525</v>

--- a/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
@@ -294,9 +294,6 @@
     <t>LED1, LED2, LED3, LED5</t>
   </si>
   <si>
-    <t>LED4, LED?</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -396,9 +393,6 @@
     <t>R169</t>
   </si>
   <si>
-    <t>R?</t>
-  </si>
-  <si>
     <t>RN1, RN2, RN3</t>
   </si>
   <si>
@@ -1651,6 +1645,12 @@
   </si>
   <si>
     <t>CS-IPS-ST7796-NTP</t>
+  </si>
+  <si>
+    <t>LED4, LED6</t>
+  </si>
+  <si>
+    <t>R89</t>
   </si>
 </sst>
 </file>
@@ -1842,7 +1842,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1905,6 +1905,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2197,7 +2200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:R125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2210,9 +2213,12 @@
     <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2221,11 +2227,14 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="23"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2237,28 +2246,28 @@
         <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -2271,26 +2280,26 @@
         <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
         <f t="shared" ref="B4:B120" si="0">ROW(B4) - ROW($B$2)</f>
@@ -2303,26 +2312,26 @@
         <v>34</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J4" s="9">
         <v>3</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -2335,26 +2344,26 @@
         <v>35</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J5" s="7">
         <v>13</v>
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -2367,28 +2376,28 @@
         <v>36</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J6" s="14">
         <v>2</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -2401,26 +2410,26 @@
         <v>37</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J7" s="7">
         <v>4</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -2433,26 +2442,26 @@
         <v>38</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
       </c>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -2465,26 +2474,26 @@
         <v>39</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J9" s="7">
         <v>20</v>
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -2497,26 +2506,26 @@
         <v>40</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J10" s="9">
         <v>8</v>
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -2529,26 +2538,26 @@
         <v>41</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -2561,26 +2570,26 @@
         <v>42</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J12" s="9">
         <v>3</v>
       </c>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
@@ -2593,26 +2602,26 @@
         <v>43</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J13" s="7">
         <v>3</v>
       </c>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -2625,26 +2634,26 @@
         <v>44</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
       </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
@@ -2657,26 +2666,26 @@
         <v>45</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J15" s="7">
         <v>3</v>
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -2689,19 +2698,19 @@
         <v>46</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J16" s="9">
         <v>2</v>
@@ -2721,19 +2730,19 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J17" s="7">
         <v>8</v>
@@ -2753,19 +2762,19 @@
         <v>48</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -2785,19 +2794,19 @@
         <v>49</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -2817,19 +2826,19 @@
         <v>50</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J20" s="9">
         <v>8</v>
@@ -2849,19 +2858,19 @@
         <v>51</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2881,19 +2890,19 @@
         <v>52</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J22" s="9">
         <v>2</v>
@@ -2913,19 +2922,19 @@
         <v>53</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -2945,19 +2954,19 @@
         <v>54</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
@@ -2977,19 +2986,19 @@
         <v>55</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
@@ -3009,19 +3018,19 @@
         <v>56</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J26" s="9">
         <v>1</v>
@@ -3041,19 +3050,19 @@
         <v>57</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
@@ -3073,19 +3082,19 @@
         <v>58</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J28" s="9">
         <v>4</v>
@@ -3105,19 +3114,19 @@
         <v>59</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J29" s="7">
         <v>2</v>
@@ -3137,19 +3146,19 @@
         <v>60</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J30" s="9">
         <v>10</v>
@@ -3169,19 +3178,19 @@
         <v>61</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
@@ -3201,19 +3210,19 @@
         <v>62</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -3233,19 +3242,19 @@
         <v>63</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J33" s="7">
         <v>2</v>
@@ -3265,19 +3274,19 @@
         <v>64</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J34" s="9">
         <v>2</v>
@@ -3297,19 +3306,19 @@
         <v>65</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J35" s="7">
         <v>3</v>
@@ -3329,19 +3338,19 @@
         <v>66</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J36" s="9">
         <v>4</v>
@@ -3361,19 +3370,19 @@
         <v>67</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J37" s="7">
         <v>8</v>
@@ -3393,19 +3402,19 @@
         <v>68</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J38" s="9">
         <v>2</v>
@@ -3425,19 +3434,19 @@
         <v>69</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J39" s="7">
         <v>7</v>
@@ -3457,19 +3466,19 @@
         <v>70</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J40" s="9">
         <v>2</v>
@@ -3489,19 +3498,19 @@
         <v>71</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F41" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="I41" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J41" s="7">
         <v>2</v>
@@ -3521,19 +3530,19 @@
         <v>72</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F42" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="I42" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J42" s="9">
         <v>4</v>
@@ -3553,19 +3562,19 @@
         <v>73</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F43" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J43" s="7">
         <v>1</v>
@@ -3585,19 +3594,19 @@
         <v>74</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
@@ -3617,19 +3626,19 @@
         <v>75</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J45" s="7">
         <v>1</v>
@@ -3649,19 +3658,19 @@
         <v>76</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J46" s="9">
         <v>1</v>
@@ -3681,19 +3690,19 @@
         <v>77</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J47" s="7">
         <v>1</v>
@@ -3713,19 +3722,19 @@
         <v>78</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F48" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J48" s="9">
         <v>1</v>
@@ -3745,19 +3754,19 @@
         <v>79</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="I49" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
@@ -3777,19 +3786,19 @@
         <v>80</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G50" s="10">
         <v>1715721</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J50" s="9">
         <v>1</v>
@@ -3809,19 +3818,19 @@
         <v>81</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J51" s="7">
         <v>7</v>
@@ -3841,19 +3850,19 @@
         <v>82</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F52" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="I52" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J52" s="9">
         <v>2</v>
@@ -3873,19 +3882,19 @@
         <v>83</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F53" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="I53" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J53" s="7">
         <v>3</v>
@@ -3905,19 +3914,19 @@
         <v>84</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F54" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="I54" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J54" s="9">
         <v>1</v>
@@ -3937,19 +3946,19 @@
         <v>85</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F55" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="I55" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
@@ -3969,19 +3978,19 @@
         <v>86</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F56" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J56" s="9">
         <v>5</v>
@@ -3999,19 +4008,19 @@
         <v>87</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F57" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="I57" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J57" s="7">
         <v>1</v>
@@ -4031,19 +4040,19 @@
         <v>88</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J58" s="9">
         <v>1</v>
@@ -4063,19 +4072,19 @@
         <v>89</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -4095,19 +4104,19 @@
         <v>90</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J60" s="9">
         <v>4</v>
@@ -4124,22 +4133,22 @@
         <v>20</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>91</v>
+        <v>542</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J61" s="7">
         <v>2</v>
@@ -4156,22 +4165,22 @@
         <v>21</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J62" s="9">
         <v>1</v>
@@ -4188,22 +4197,22 @@
         <v>21</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J63" s="7">
         <v>1</v>
@@ -4220,29 +4229,29 @@
         <v>21</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J64" s="9">
         <v>1</v>
       </c>
       <c r="K64" s="9"/>
     </row>
-    <row r="65" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f>ROW(B65) - ROW($B$2)</f>
@@ -4252,29 +4261,29 @@
         <v>22</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J65" s="7">
         <v>4</v>
       </c>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="0"/>
@@ -4284,29 +4293,29 @@
         <v>22</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J66" s="9">
         <v>3</v>
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f>ROW(B67) - ROW($B$2)</f>
@@ -4316,29 +4325,29 @@
         <v>22</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J67" s="7">
         <v>29</v>
       </c>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:14" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19"/>
       <c r="B68" s="11">
         <f t="shared" si="0"/>
@@ -4348,33 +4357,37 @@
         <v>23</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I68" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J68" s="14">
         <v>2</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="M68"/>
       <c r="N68"/>
-    </row>
-    <row r="69" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="Q68"/>
+      <c r="R68"/>
+    </row>
+    <row r="69" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f>ROW(B69) - ROW($B$2)</f>
@@ -4384,29 +4397,29 @@
         <v>22</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J69" s="7">
         <v>25</v>
       </c>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" spans="1:14" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19"/>
       <c r="B70" s="11">
         <f t="shared" si="0"/>
@@ -4416,33 +4429,37 @@
         <v>22</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J70" s="14">
         <v>2</v>
       </c>
       <c r="K70" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="M70"/>
       <c r="N70"/>
-    </row>
-    <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="Q70"/>
+      <c r="R70"/>
+    </row>
+    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f>ROW(B71) - ROW($B$2)</f>
@@ -4452,29 +4469,29 @@
         <v>22</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J71" s="7">
         <v>2</v>
       </c>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f t="shared" si="0"/>
@@ -4484,29 +4501,29 @@
         <v>22</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J72" s="9">
         <v>13</v>
       </c>
       <c r="K72" s="9"/>
     </row>
-    <row r="73" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f>ROW(B73) - ROW($B$2)</f>
@@ -4516,29 +4533,29 @@
         <v>22</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J73" s="7">
         <v>34</v>
       </c>
       <c r="K73" s="7"/>
     </row>
-    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f t="shared" si="0"/>
@@ -4548,29 +4565,29 @@
         <v>22</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J74" s="9">
         <v>1</v>
       </c>
       <c r="K74" s="9"/>
     </row>
-    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f>ROW(B75) - ROW($B$2)</f>
@@ -4580,29 +4597,29 @@
         <v>22</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J75" s="7">
         <v>1</v>
       </c>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f t="shared" si="0"/>
@@ -4612,29 +4629,29 @@
         <v>22</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
       </c>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f>ROW(B77) - ROW($B$2)</f>
@@ -4644,29 +4661,29 @@
         <v>22</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J77" s="7">
         <v>1</v>
       </c>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f t="shared" si="0"/>
@@ -4676,29 +4693,29 @@
         <v>22</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J78" s="9">
         <v>1</v>
       </c>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f>ROW(B79) - ROW($B$2)</f>
@@ -4708,29 +4725,29 @@
         <v>22</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J79" s="7">
         <v>2</v>
       </c>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="0"/>
@@ -4740,27 +4757,27 @@
         <v>22</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J80" s="9">
         <v>4</v>
       </c>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f>ROW(B81) - ROW($B$2)</f>
@@ -4770,29 +4787,29 @@
         <v>22</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J81" s="7">
         <v>2</v>
       </c>
       <c r="K81" s="7"/>
     </row>
-    <row r="82" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f t="shared" si="0"/>
@@ -4802,29 +4819,29 @@
         <v>22</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J82" s="9">
         <v>1</v>
       </c>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f>ROW(B83) - ROW($B$2)</f>
@@ -4834,29 +4851,29 @@
         <v>22</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J83" s="7">
         <v>12</v>
       </c>
       <c r="K83" s="7"/>
     </row>
-    <row r="84" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f t="shared" si="0"/>
@@ -4866,29 +4883,29 @@
         <v>22</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J84" s="9">
         <v>1</v>
       </c>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f>ROW(B85) - ROW($B$2)</f>
@@ -4898,29 +4915,29 @@
         <v>22</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J85" s="7">
         <v>2</v>
       </c>
       <c r="K85" s="7"/>
     </row>
-    <row r="86" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="0"/>
@@ -4930,321 +4947,325 @@
         <v>22</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J86" s="9">
         <v>1</v>
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f>ROW(B87) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>23</v>
+      <c r="C87" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>117</v>
+        <v>543</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J87" s="7">
         <v>1</v>
       </c>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B88) - ROW($B$2)</f>
         <v>86</v>
       </c>
-      <c r="C88" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I88" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="J88" s="9">
-        <v>10</v>
-      </c>
-      <c r="K88" s="9"/>
-    </row>
-    <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="J88" s="7">
+        <v>1</v>
+      </c>
+      <c r="K88" s="7"/>
+    </row>
+    <row r="89" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
-        <f>ROW(B89) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D89" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="J89" s="7">
-        <v>3</v>
-      </c>
-      <c r="K89" s="7"/>
-    </row>
-    <row r="90" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D89" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="J89" s="9">
+        <v>10</v>
+      </c>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B90) - ROW($B$2)</f>
         <v>88</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I90" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="J90" s="9">
-        <v>2</v>
-      </c>
-      <c r="K90" s="9"/>
-    </row>
-    <row r="91" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D90" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="J90" s="7">
+        <v>3</v>
+      </c>
+      <c r="K90" s="7"/>
+    </row>
+    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
-        <f>ROW(B91) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D91" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="J91" s="7">
-        <v>4</v>
-      </c>
-      <c r="K91" s="7"/>
-    </row>
-    <row r="92" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D91" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="I91" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="J91" s="9">
+        <v>2</v>
+      </c>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B92) - ROW($B$2)</f>
         <v>90</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I92" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="J92" s="9">
-        <v>1</v>
-      </c>
-      <c r="K92" s="9"/>
-    </row>
-    <row r="93" spans="1:14" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D92" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="J92" s="7">
+        <v>4</v>
+      </c>
+      <c r="K92" s="7"/>
+    </row>
+    <row r="93" spans="1:18" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="19"/>
       <c r="B93" s="11">
-        <f>ROW(B93) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D93" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E93" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="F93" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="G93" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="H93" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="I93" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="J93" s="17">
+      <c r="D93" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="I93" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="J93" s="9">
         <v>1</v>
       </c>
-      <c r="K93" s="16" t="s">
-        <v>524</v>
-      </c>
+      <c r="K93" s="9"/>
       <c r="M93"/>
       <c r="N93"/>
-    </row>
-    <row r="94" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O93"/>
+      <c r="P93"/>
+      <c r="Q93"/>
+      <c r="R93"/>
+    </row>
+    <row r="94" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B94) - ROW($B$2)</f>
         <v>92</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D94" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I94" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="J94" s="9">
+      <c r="D94" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F94" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="H94" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="I94" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="J94" s="17">
         <v>1</v>
       </c>
-      <c r="K94" s="9"/>
-    </row>
-    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K94" s="16" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
-        <f>ROW(B95) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="J95" s="7">
+      <c r="D95" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="J95" s="9">
         <v>1</v>
       </c>
-      <c r="K95" s="7"/>
-    </row>
-    <row r="96" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K95" s="9"/>
+    </row>
+    <row r="96" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f t="shared" si="0"/>
@@ -5254,22 +5275,22 @@
         <v>24</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J96" s="9">
         <v>3</v>
@@ -5286,22 +5307,22 @@
         <v>25</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F97" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="I97" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J97" s="7">
         <v>3</v>
@@ -5318,22 +5339,22 @@
         <v>25</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F98" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="I98" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J98" s="9">
         <v>4</v>
@@ -5350,22 +5371,22 @@
         <v>26</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F99" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I99" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J99" s="7">
         <v>1</v>
@@ -5382,22 +5403,22 @@
         <v>27</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J100" s="9">
         <v>1</v>
@@ -5414,22 +5435,22 @@
         <v>28</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J101" s="7">
         <v>1</v>
@@ -5446,22 +5467,22 @@
         <v>29</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J102" s="9">
         <v>1</v>
@@ -5478,22 +5499,22 @@
         <v>29</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J103" s="7">
         <v>1</v>
@@ -5510,22 +5531,22 @@
         <v>29</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J104" s="9">
         <v>1</v>
@@ -5542,22 +5563,22 @@
         <v>29</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J105" s="7">
         <v>1</v>
@@ -5574,22 +5595,22 @@
         <v>29</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J106" s="9">
         <v>1</v>
@@ -5606,22 +5627,22 @@
         <v>29</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J107" s="7">
         <v>2</v>
@@ -5638,22 +5659,22 @@
         <v>29</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J108" s="9">
         <v>1</v>
@@ -5670,22 +5691,22 @@
         <v>30</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J109" s="7">
         <v>1</v>
@@ -5702,22 +5723,22 @@
         <v>29</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J110" s="9">
         <v>1</v>
@@ -5734,22 +5755,22 @@
         <v>29</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J111" s="7">
         <v>1</v>
@@ -5766,22 +5787,22 @@
         <v>29</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J112" s="9">
         <v>3</v>
@@ -5798,22 +5819,22 @@
         <v>29</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J113" s="7">
         <v>1</v>
@@ -5830,22 +5851,22 @@
         <v>29</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F114" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="I114" s="8" t="s">
         <v>523</v>
-      </c>
-      <c r="G114" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="H114" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="J114" s="9">
         <v>1</v>
@@ -5862,28 +5883,28 @@
         <v>31</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H115" s="14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J115" s="14">
         <v>1</v>
       </c>
       <c r="K115" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5896,22 +5917,22 @@
         <v>31</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="J116" s="9">
         <v>1</v>
@@ -5928,22 +5949,22 @@
         <v>31</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J117" s="7">
         <v>1</v>
@@ -5960,22 +5981,22 @@
         <v>31</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J118" s="9">
         <v>1</v>
@@ -5988,31 +6009,31 @@
         <v>117</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F119" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="H119" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="G119" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>525</v>
-      </c>
       <c r="I119" s="21" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J119" s="9">
         <v>1</v>
       </c>
       <c r="K119" s="22" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6021,25 +6042,25 @@
         <v>118</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D120" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G120" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="E120" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="F120" s="7" t="s">
+      <c r="H120" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="I120" s="21" t="s">
         <v>523</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="I120" s="21" t="s">
-        <v>525</v>
       </c>
       <c r="J120" s="9">
         <v>8</v>
@@ -6052,25 +6073,25 @@
         <v>119</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G121" s="8">
         <v>50173</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I121" s="21" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J121" s="9">
         <v>2</v>
@@ -6083,25 +6104,25 @@
         <v>120</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E122" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="H122" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="F122" s="7" t="s">
+      <c r="I122" s="21" t="s">
         <v>523</v>
-      </c>
-      <c r="G122" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="I122" s="21" t="s">
-        <v>525</v>
       </c>
       <c r="J122" s="9">
         <v>1</v>
@@ -6114,25 +6135,25 @@
         <v>121</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D123" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G123" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="E123" s="9" t="s">
+      <c r="H123" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="F123" s="7" t="s">
+      <c r="I123" s="21" t="s">
         <v>523</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="I123" s="21" t="s">
-        <v>525</v>
       </c>
       <c r="J123" s="9">
         <v>1</v>

--- a/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
+++ b/Design Files/Control-Board-v1.0/BOM/Client-BOM-Control-Board-v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\muhunthancanagey-servocontrol\Design Files\Control-Board-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="594">
   <si>
     <t>#</t>
   </si>
@@ -57,6 +57,9 @@
     <t>Connector</t>
   </si>
   <si>
+    <t>Ethernet Connectors</t>
+  </si>
+  <si>
     <t>Male Header</t>
   </si>
   <si>
@@ -69,15 +72,15 @@
     <t>Connectors (RJ45 RJ11)</t>
   </si>
   <si>
+    <t>FFC/FPC Connector</t>
+  </si>
+  <si>
+    <t>Terminal Block</t>
+  </si>
+  <si>
     <t>RJ45 Connector</t>
   </si>
   <si>
-    <t>FFC/FPC Connector</t>
-  </si>
-  <si>
-    <t>Terminal Block</t>
-  </si>
-  <si>
     <t>Inductor</t>
   </si>
   <si>
@@ -93,16 +96,16 @@
     <t>Resistors</t>
   </si>
   <si>
-    <t>Resistor Array</t>
-  </si>
-  <si>
     <t>Switch</t>
   </si>
   <si>
     <t>DIP Switches</t>
   </si>
   <si>
-    <t>Module</t>
+    <t>DIP Switche</t>
+  </si>
+  <si>
+    <t>RJ45 Transformer</t>
   </si>
   <si>
     <t>Microcontrollers</t>
@@ -111,37 +114,43 @@
     <t>IC</t>
   </si>
   <si>
-    <t>TVS Diode</t>
-  </si>
-  <si>
     <t>Crystal</t>
   </si>
   <si>
+    <t>Oscillators</t>
+  </si>
+  <si>
     <t>Designator</t>
   </si>
   <si>
     <t>C1, C8</t>
   </si>
   <si>
-    <t>C2, C69, C76</t>
-  </si>
-  <si>
-    <t>C3, C5, C12, C13, C28, C29, C30, C33, C34, C36, C37, C40, C58</t>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
   </si>
   <si>
     <t>C4, C6</t>
   </si>
   <si>
+    <t>C5, C60</t>
+  </si>
+  <si>
     <t>C7, C11, C89, C90</t>
   </si>
   <si>
     <t>C9</t>
   </si>
   <si>
-    <t>C10, C14, C15, C16, C24, C49, C50, C51, C52, C53, C54, C55, C56, C57, C59, C62, C63, C64, C88, C96</t>
-  </si>
-  <si>
-    <t>C17, C27, C70, C71, C72, C73, C74, C75</t>
+    <t>C10, C14, C15, C24, C49, C50, C51, C52, C53, C54, C55, C56, C57, C59, C62, C63, C64, C88, C96</t>
+  </si>
+  <si>
+    <t>C12, C13, C28, C29, C30, C33, C34, C36, C37, C40, C58, C67, C68, C70, C71, C72, C74, C75, C79, C81, C82, C83, C84, C104</t>
+  </si>
+  <si>
+    <t>C17, C27</t>
   </si>
   <si>
     <t>C18</t>
@@ -156,7 +165,10 @@
     <t>C23</t>
   </si>
   <si>
-    <t>C25, C31, C68</t>
+    <t>C25, C31, C69, C73, C78, C80</t>
+  </si>
+  <si>
+    <t>C26, C76, C97</t>
   </si>
   <si>
     <t>C35, C38</t>
@@ -165,43 +177,37 @@
     <t>C41, C42, C43, C44, C45, C46, C47, C48</t>
   </si>
   <si>
-    <t>C60</t>
-  </si>
-  <si>
     <t>C61</t>
   </si>
   <si>
     <t>C65, C66, C85, C86, C91, C92, C93, C94</t>
   </si>
   <si>
-    <t>C67</t>
-  </si>
-  <si>
-    <t>C77, C78</t>
-  </si>
-  <si>
-    <t>C79, C83</t>
-  </si>
-  <si>
-    <t>C80</t>
-  </si>
-  <si>
-    <t>C81, C82</t>
-  </si>
-  <si>
-    <t>C84</t>
+    <t>C77, C98</t>
   </si>
   <si>
     <t>C87, C95</t>
   </si>
   <si>
+    <t>C99</t>
+  </si>
+  <si>
+    <t>C100</t>
+  </si>
+  <si>
+    <t>C101</t>
+  </si>
+  <si>
+    <t>C102, C103</t>
+  </si>
+  <si>
     <t>D1, D2, D3, D4</t>
   </si>
   <si>
     <t>D5, D6</t>
   </si>
   <si>
-    <t>D7, D8, D9, D10, D11, D12, D13, D14, D15, D16</t>
+    <t>D7, D8, D9, D10, D11, D12, D13, D14, D15, D16, D18, D31, D32, D33</t>
   </si>
   <si>
     <t>D17</t>
@@ -243,6 +249,9 @@
     <t>J3</t>
   </si>
   <si>
+    <t>J8, J16</t>
+  </si>
+  <si>
     <t>J9</t>
   </si>
   <si>
@@ -270,9 +279,6 @@
     <t>J18, J22</t>
   </si>
   <si>
-    <t>J21, J34, J35</t>
-  </si>
-  <si>
     <t>J24</t>
   </si>
   <si>
@@ -282,6 +288,9 @@
     <t>J29, J30, J31, J32, J33</t>
   </si>
   <si>
+    <t>J34, J35</t>
+  </si>
+  <si>
     <t>J36</t>
   </si>
   <si>
@@ -291,28 +300,37 @@
     <t>L2</t>
   </si>
   <si>
-    <t>LED1, LED2, LED3, LED5</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Q2</t>
+    <t>LED1, LED2, LED3, LED5, LED6, LED7, LED8</t>
+  </si>
+  <si>
+    <t>LED4, LED9</t>
+  </si>
+  <si>
+    <t>LED10</t>
+  </si>
+  <si>
+    <t>LED11</t>
+  </si>
+  <si>
+    <t>Q1, Q2</t>
   </si>
   <si>
     <t>Q3</t>
   </si>
   <si>
-    <t>R1, R2, R15, R16</t>
-  </si>
-  <si>
-    <t>R3, R17, R85</t>
-  </si>
-  <si>
-    <t>R4, R5, R6, R7, R8, R20, R25, R32, R33, R34, R35, R36, R39, R40, R41, R63, R64, R73, R81, R83, R91, R92, R102, R144, R157, R165, R166, R167, R168</t>
-  </si>
-  <si>
-    <t>R9, R12</t>
+    <t>R1, R2, R15, R16, R190, R215, R216</t>
+  </si>
+  <si>
+    <t>R3, R17</t>
+  </si>
+  <si>
+    <t>R4, R5, R6, R7, R20, R25, R32, R33, R34, R35, R39, R40, R41, R63, R64, R76, R77, R91, R92, R102, R144, R157, R165, R166, R167, R168, R173, R176, R191, R213, R240, R241, R242, R243, R244, R245, R246, R247, R248, R249, R250, R251</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9, R12, R227</t>
   </si>
   <si>
     <t>R10, R11, R21, R22, R103, R104, R105, R106, R107, R116, R122, R123, R124, R125, R126, R127, R128, R129, R130, R131, R140, R141, R159, R161, R162</t>
@@ -321,13 +339,13 @@
     <t>R13, R14</t>
   </si>
   <si>
-    <t>R18, R19</t>
-  </si>
-  <si>
-    <t>R23, R24, R26, R27, R28, R29, R30, R31, R74, R75, R76, R79, R101</t>
-  </si>
-  <si>
-    <t>R37, R38, R49, R50, R52, R53, R57, R58, R60, R62, R65, R66, R67, R68, R69, R70, R71, R93, R94, R95, R96, R98, R99, R100, R108, R109, R111, R114, R115, R118, R132, R133, R138, R139</t>
+    <t>R18, R19, R87, R88, R90, R170, R171, R172, R174, R175</t>
+  </si>
+  <si>
+    <t>R23, R24, R26, R27, R28, R29, R30, R31, R89, R101, R231, R232, R233</t>
+  </si>
+  <si>
+    <t>R36, R37, R38, R49, R50, R52, R53, R57, R58, R60, R62, R65, R66, R67, R68, R69, R70, R71, R93, R94, R95, R96, R98, R99, R100, R108, R109, R111, R114, R115, R118, R132, R133, R138, R139, R207, R209, R210, R211, R212, R228, R229, R230, R234, R235</t>
   </si>
   <si>
     <t>R42</t>
@@ -357,16 +375,16 @@
     <t>R72</t>
   </si>
   <si>
-    <t>R77, R78, R80, R82, R145, R146, R147, R148, R151, R152, R153, R154</t>
-  </si>
-  <si>
-    <t>R84</t>
-  </si>
-  <si>
-    <t>R86, R88</t>
-  </si>
-  <si>
-    <t>R87</t>
+    <t>R73, R75, R177, R181, R192, R198</t>
+  </si>
+  <si>
+    <t>R74</t>
+  </si>
+  <si>
+    <t>R78, R81, R82, R83, R84, R85, R86, R145, R146, R147, R148, R151, R152, R153, R154, R183, R184, R185, R186, R200, R201, R202, R203</t>
+  </si>
+  <si>
+    <t>R79, R80</t>
   </si>
   <si>
     <t>R97</t>
@@ -393,10 +411,31 @@
     <t>R169</t>
   </si>
   <si>
-    <t>RN1, RN2, RN3</t>
-  </si>
-  <si>
-    <t>SW1, SW6, SW8</t>
+    <t>R178, R179, R180, R182, R188, R189, R194, R196, R197, R199, R205, R206</t>
+  </si>
+  <si>
+    <t>R187, R204</t>
+  </si>
+  <si>
+    <t>R193, R217, R218, R219, R220, R221, R222, R223, R224, R225, R226</t>
+  </si>
+  <si>
+    <t>R195</t>
+  </si>
+  <si>
+    <t>R208</t>
+  </si>
+  <si>
+    <t>R214</t>
+  </si>
+  <si>
+    <t>R236, R238, R239</t>
+  </si>
+  <si>
+    <t>R237</t>
+  </si>
+  <si>
+    <t>SW1, SW6, SW8, SW9</t>
   </si>
   <si>
     <t>SW2, SW3, SW4, SW5</t>
@@ -405,6 +444,15 @@
     <t>SW7</t>
   </si>
   <si>
+    <t>SW10</t>
+  </si>
+  <si>
+    <t>SW11</t>
+  </si>
+  <si>
+    <t>T1, T2</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
@@ -417,7 +465,7 @@
     <t>U4</t>
   </si>
   <si>
-    <t>U5</t>
+    <t>U6</t>
   </si>
   <si>
     <t>U7</t>
@@ -450,6 +498,9 @@
     <t>U19</t>
   </si>
   <si>
+    <t>U20</t>
+  </si>
+  <si>
     <t>X1</t>
   </si>
   <si>
@@ -462,84 +513,90 @@
     <t>X4</t>
   </si>
   <si>
+    <t>X5</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
     <t>CAP CER 4700PF 50V C0G/NPO 0603</t>
   </si>
   <si>
+    <t>CAP CER 1UF 25V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 16V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 30PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 10V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X5R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 47PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
+    <t>CAP ALUM 220UF 20% 50V SMD</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 16V X5R 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 50V X5R 1206</t>
+  </si>
+  <si>
+    <t>CAP CER 22UF 25V X5R 0805</t>
+  </si>
+  <si>
     <t>CAP CER 10UF 16V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 16V X7R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 30PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 10V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 50V X7R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 50V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 47PF 50V C0G/NP0 0402</t>
-  </si>
-  <si>
-    <t>CAP ALUM 220UF 20% 50V SMD</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 16V X5R 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 10UF 50V X5R 1206</t>
-  </si>
-  <si>
-    <t>CAP CER 22UF 25V X5R 0805</t>
-  </si>
-  <si>
     <t>CAP CER 4700PF 50V X7R 0402</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 100V X5R 0402</t>
   </si>
   <si>
-    <t>CAP CER 1UF 16V X5R 0402</t>
-  </si>
-  <si>
     <t>50V 470pF ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
   </si>
   <si>
     <t>CAP CER 10PF 50V C0G/NP0 0402</t>
   </si>
   <si>
-    <t>CAP CER 22UF 35V X5R 0805</t>
-  </si>
-  <si>
-    <t>50V 6.8nF X7R ±10% 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 10000PF 50V C0G/NPO 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 0.022UF 50V X7R 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 12PF 50V C0G/NPO 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 10V X5R 0603</t>
+    <t>CAP CER 1000PF 2KV X7R 1206</t>
   </si>
   <si>
     <t>CAP CER 0.022UF 16V X7R 0402</t>
   </si>
   <si>
+    <t>CAP CER 100PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 1000PF 25V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 10000PF 25V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 18PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
     <t>TVS DIODE 5V 9.8V SOD923</t>
   </si>
   <si>
@@ -576,7 +633,7 @@
     <t>FERRITE BEAD 220 OHM 0603 1LN</t>
   </si>
   <si>
-    <t>100mΩ ±25% 300Ω@100MHz 0805 Ferrite Beads ROHS</t>
+    <t>Ferrite Beads Multi-Layer 120Ohm 25% 100MHz 2A 50mOhm DCR 0603 Paper T/R</t>
   </si>
   <si>
     <t>5A 1 16P Female Type-C SMD USB Connectors ROHS</t>
@@ -588,7 +645,10 @@
     <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
-    <t>Gold 250V 3A Policy 2.5mm 9P 260℃ -40℃~+105℃ 2.54mm Single Row Black Brass 1x9P 2.54mm Plugin,P=2.54mm Pin Headers ROHS</t>
+    <t>CONN MOD JACK 8P8C R/A SHIELDED</t>
+  </si>
+  <si>
+    <t>Gold 250V 3A Policy 2.5mm 14P 260℃ -40℃~+105℃ 2.54mm Single Row Black Brass 2.54mm 1x14P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
     <t>CONN HEADER VERT 3POS 2.54MM</t>
@@ -615,18 +675,18 @@
     <t>RJ45Receptacle Unshielded 1 Bend insert 260℃ Gold Phosphor Bronze Without LED -40℃~+85℃ Plugin Ethernet Connectors / Modular Connectors (RJ45 RJ11) ROHS</t>
   </si>
   <si>
+    <t>Slide Lock 32P Contact,Top Surface Mount，Right Angle 0.5mm SMD,P=0.5mm,Surface Mount，Right Angle FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 4POS 2.5MM</t>
+  </si>
+  <si>
+    <t>1x3P 18A -40℃~+105℃ 250V Black 12~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
+  </si>
+  <si>
     <t>RJ45 RJReceptacle 1 WithLED Plugin Ethernet Connectors/Modular Connectors (RJ45 RJ11) ROHS</t>
   </si>
   <si>
-    <t>Slide Lock 32P Contact,Top Surface Mount，Right Angle 0.5mm SMD,P=0.5mm,Surface Mount，Right Angle FFC/FPC Connectors ROHS</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 4POS 2.5MM</t>
-  </si>
-  <si>
-    <t>1x3P 18A -40℃~+105℃ 250V Black 12~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
-  </si>
-  <si>
     <t>M4 Plugin PCB Welding Terminal ROHS</t>
   </si>
   <si>
@@ -642,10 +702,13 @@
     <t>Emerald 0603 Light Emitting Diodes (LED) ROHS</t>
   </si>
   <si>
-    <t>NPN 246mW 100mA 50V SOT-23 Digital Transistors ROHS</t>
-  </si>
-  <si>
-    <t>20V 2.2A 800mW 110mΩ@4.5V,2.7A 810mV@250uA P Channel SOT-23 MOSFETs ROHS</t>
+    <t>20mA 100mcd~220mcd 600nm~610nm -30℃~+85℃ Orange 130° 65mW 1.6V~2.6V 0603 Light Emitting Diodes (LED) ROHS</t>
+  </si>
+  <si>
+    <t>yellow 0603 Light Emitting Diodes (LED) ROHS</t>
+  </si>
+  <si>
+    <t>25V 300mW 120@100mA,1V 1.5A NPN SOT-23 Bipolar Transistors - BJT ROHS</t>
   </si>
   <si>
     <t>50V 220mA 3.5Ω@10V,220mA 225mW 1.6V@1mA N Channel SOT-23 MOSFETs ROHS</t>
@@ -660,6 +723,9 @@
     <t>RES 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
+    <t>RES 2K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
     <t>RES 0 OHM JUMPER 1/16W 0402</t>
   </si>
   <si>
@@ -696,21 +762,18 @@
     <t>RES 100K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES SMD 1K OHM 1% 1/5W 0402</t>
+    <t>RES 22.1K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES SMD 220 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 47.5K OHM 1% 1/10W 0603</t>
   </si>
   <si>
     <t>RES 49.9 OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES SMD 10 OHM 1% 1/5W 0402</t>
-  </si>
-  <si>
-    <t>SMD Chip Resistor, 330 Ohm, ± 1%, 63 mW, 0402 [1005 Metric], Thick Film, General Purpose</t>
-  </si>
-  <si>
-    <t>RES SMD 12.4K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES 2.2 OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -732,10 +795,25 @@
     <t>RES SMD 10K OHM 1% 1/20W 0201</t>
   </si>
   <si>
-    <t>RES SMD 220 OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES ARRAY 4 RES 10K OHM 1206</t>
+    <t>RES SMD 51R 100mW 0603</t>
+  </si>
+  <si>
+    <t>RES 75 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 1K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES SMD 11.8K OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 1M OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 240 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 100 OHM 1% 1/16W 0402</t>
   </si>
   <si>
     <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
@@ -747,19 +825,28 @@
     <t>3 positions SPST Black Flat Toggle, Raised Style SMD-6P,6x7.6mm DIP Switches ROHS</t>
   </si>
   <si>
-    <t>SMD MODULE, ESP32-S3R8 WITH 3.3V</t>
+    <t>7Bit SPST 24V 25mA Black 3千次 Slide (Standard),凸起式 SMD-14P,6x17.8mm DIP Switches ROHS</t>
+  </si>
+  <si>
+    <t>Gull Wing SPST 24V 25mA Black -20℃~+70℃ 3000 Flat dial, raised type 2.54mm 5 SMD-10P,6x12.6mm DIP Switches ROHS</t>
+  </si>
+  <si>
+    <t>XFRMR MAGNETIC 1PORT 1:1 10/100</t>
+  </si>
+  <si>
+    <t>Full Speed USB to UART Bridge USB 2.0 3.3V T/R Automotive 28-Pin QFN EP</t>
   </si>
   <si>
     <t>IC MCU 32BIT 512KB FLASH 64LQFP</t>
   </si>
   <si>
-    <t>IC XPNDR 100KHZ I2C 20TSSOP</t>
+    <t>IC XPNDR 1.7MHZ I2C 28SSOP</t>
   </si>
   <si>
     <t>IC ADC 16BIT SIGMA-DELTA 10VSSOP</t>
   </si>
   <si>
-    <t>400kHz SO-8 I/O Expanders ROHS</t>
+    <t>RX TXRX MOD WIFI TRACE ANT SMD</t>
   </si>
   <si>
     <t>IC REG BUCK ADJ 3A TSOT26</t>
@@ -771,10 +858,10 @@
     <t>IC TRANSCEIVER HALF 1/1 14VSON</t>
   </si>
   <si>
-    <t>SPI LQFP-48(7x7) Ethernet ICs ROHS</t>
-  </si>
-  <si>
-    <t>TVS DIODE 5.5VWM 8.5VC SOT23-5</t>
+    <t>8-bit I2C IO Expander 20TSSOP</t>
+  </si>
+  <si>
+    <t>IC EEPROM 2KBIT I2C 1MHZ 8SOIC</t>
   </si>
   <si>
     <t>IC TRANSLTR BIDIRECTIONAL 8VSSOP</t>
@@ -792,6 +879,9 @@
     <t>IC EEPROM 256KBIT I2C 1MHZ 8SOIC</t>
   </si>
   <si>
+    <t>IC ETHERNET SWITCH 3PORT 48-LQFP</t>
+  </si>
+  <si>
     <t>32.768kHz 12.5pF ±20ppm MC-306 Crystals ROHS</t>
   </si>
   <si>
@@ -801,6 +891,9 @@
     <t>25MHz 贴片晶振 18pF ±10ppm ±20ppm SMD3225-4P Crystals ROHS</t>
   </si>
   <si>
+    <t>XTAL OSC XO 25.0000MHZ CMOS SMD</t>
+  </si>
+  <si>
     <t>CRYSTAL 25.0000MHZ 12PF SMD</t>
   </si>
   <si>
@@ -855,13 +948,13 @@
     <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
-    <t>Ind-0805</t>
-  </si>
-  <si>
     <t>HC-XH-2A-G</t>
   </si>
   <si>
-    <t>HDR 1X9 male</t>
+    <t>2-406549-1</t>
+  </si>
+  <si>
+    <t>HDR 1x14 TH Male</t>
   </si>
   <si>
     <t>HDR1X3_</t>
@@ -882,15 +975,15 @@
     <t>X12ADIWA3DY1027</t>
   </si>
   <si>
+    <t>AFC07-S32ECA-00</t>
+  </si>
+  <si>
+    <t>DB128L-5.08-3P-BK-S</t>
+  </si>
+  <si>
     <t>HR911105A</t>
   </si>
   <si>
-    <t>AFC07-S32ECA-00</t>
-  </si>
-  <si>
-    <t>DB128L-5.08-3P-BK-S</t>
-  </si>
-  <si>
     <t>T44001</t>
   </si>
   <si>
@@ -912,685 +1005,751 @@
     <t>Res-0201</t>
   </si>
   <si>
-    <t>YC164-FR-0710KL</t>
-  </si>
-  <si>
     <t>B3U-1000P</t>
   </si>
   <si>
     <t>DSIC03LSGET</t>
   </si>
   <si>
-    <t>41-SMD Module</t>
+    <t>DSIC07LS-P</t>
+  </si>
+  <si>
+    <t>28-QFN (5x5)_</t>
   </si>
   <si>
     <t>LQFP-64(10x10)</t>
   </si>
   <si>
+    <t>SSOP-28-208mil</t>
+  </si>
+  <si>
+    <t>VSSOP-10</t>
+  </si>
+  <si>
+    <t>38-SMD Module</t>
+  </si>
+  <si>
+    <t>SOT- 223</t>
+  </si>
+  <si>
+    <t>VSON-14(3x4.5)</t>
+  </si>
+  <si>
     <t>TSSOP-20</t>
   </si>
   <si>
-    <t>VSSOP-10</t>
-  </si>
-  <si>
-    <t>SOP-8</t>
+    <t>SOIC-8(0.154", 3.90mm Width)</t>
+  </si>
+  <si>
+    <t>VSSOP-8(3.1x2.1)</t>
+  </si>
+  <si>
+    <t>SON-8-EP(3x3)</t>
+  </si>
+  <si>
+    <t>QFN-64-EP(9x9)</t>
+  </si>
+  <si>
+    <t>CAT24C256WI-GT3</t>
+  </si>
+  <si>
+    <t>48-LQFP (7x7)</t>
+  </si>
+  <si>
+    <t>MC-306</t>
+  </si>
+  <si>
+    <t>SMD3225-4P</t>
+  </si>
+  <si>
+    <t>SMD2520-4P</t>
+  </si>
+  <si>
+    <t>Q22FA12800090</t>
+  </si>
+  <si>
+    <t>Manufacturer Part Number</t>
+  </si>
+  <si>
+    <t>CC0603JRNPO9BN472</t>
+  </si>
+  <si>
+    <t>CL05A105KA5NQNC</t>
+  </si>
+  <si>
+    <t>CL10A475KA8NQNC</t>
+  </si>
+  <si>
+    <t>CC0402CRNPO9BN6R8</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R7BB105</t>
+  </si>
+  <si>
+    <t>CC0402GRNPO9BN300</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB475</t>
+  </si>
+  <si>
+    <t>C1005X7R1H104KT000F</t>
+  </si>
+  <si>
+    <t>CC0402JRX7R7BB104</t>
+  </si>
+  <si>
+    <t>C1005X5R1H104K050BB</t>
+  </si>
+  <si>
+    <t>GCM1555C1H470FA16D</t>
+  </si>
+  <si>
+    <t>UCD1H221MNL1GS</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R7BB475</t>
+  </si>
+  <si>
+    <t>CC1206KKX5R9BB106</t>
+  </si>
+  <si>
+    <t>CC0805MKX5R8BB226</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R7BB106</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R9BB472</t>
+  </si>
+  <si>
+    <t>GRM155R62A104KE14D</t>
+  </si>
+  <si>
+    <t>GRM155R11H471KA01D</t>
+  </si>
+  <si>
+    <t>GRM1555C1H100JA01D</t>
+  </si>
+  <si>
+    <t>CC1206KKX7RDBB102</t>
+  </si>
+  <si>
+    <t>CC0402JRX7R7BB223</t>
+  </si>
+  <si>
+    <t>CC0402JRNPO9BN101</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R8BB102</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R8BB103</t>
+  </si>
+  <si>
+    <t>GCM1555C1H180GA16D</t>
+  </si>
+  <si>
+    <t>ESD9L5.0ST5G</t>
+  </si>
+  <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>MM3Z3V3</t>
+  </si>
+  <si>
+    <t>SS56</t>
+  </si>
+  <si>
+    <t>SMBJ28A-13-F</t>
+  </si>
+  <si>
+    <t>PESD5V0H1BSFYL</t>
+  </si>
+  <si>
+    <t>CDSOT23-T24CAN-Q</t>
+  </si>
+  <si>
+    <t>SM712</t>
+  </si>
+  <si>
+    <t>SMBJ8.0CA</t>
+  </si>
+  <si>
+    <t>MF-MSMF010-2</t>
+  </si>
+  <si>
+    <t>SMD0805P020TF</t>
+  </si>
+  <si>
+    <t>BLM18PG221SN1D</t>
+  </si>
+  <si>
+    <t>BLM18PG121SN1D</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>C145963</t>
+  </si>
+  <si>
+    <t>X6511WV-14H-C60D30</t>
+  </si>
+  <si>
+    <t>X6511WV-05H-C60D30</t>
+  </si>
+  <si>
+    <t>X6511WV-04H-C60D30</t>
+  </si>
+  <si>
+    <t>B3B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>X6511WV-02H-C60D30</t>
+  </si>
+  <si>
+    <t>B4B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>BLM15AG601SN1D</t>
+  </si>
+  <si>
+    <t>0630CDMCCDS-6R8MC</t>
+  </si>
+  <si>
+    <t>NCD0603R3</t>
+  </si>
+  <si>
+    <t>NCD0603G2</t>
+  </si>
+  <si>
+    <t>NCD0603O2</t>
+  </si>
+  <si>
+    <t>NCD0603Y2</t>
+  </si>
+  <si>
+    <t>SS8050-G</t>
+  </si>
+  <si>
+    <t>BSS138</t>
+  </si>
+  <si>
+    <t>RC0402FR-075K1L</t>
+  </si>
+  <si>
+    <t>AF0402JR-071ML</t>
+  </si>
+  <si>
+    <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-074K7L</t>
+  </si>
+  <si>
+    <t>RC0603JR-070RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-0733RL</t>
+  </si>
+  <si>
+    <t>RT0402BRE07158KL</t>
+  </si>
+  <si>
+    <t>RT0402BRD0730K1L</t>
+  </si>
+  <si>
+    <t>RC0402FR-073K9L</t>
+  </si>
+  <si>
+    <t>RC0402FR-07470RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07200RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-0733KL</t>
+  </si>
+  <si>
+    <t>RTT0360R4FTP</t>
+  </si>
+  <si>
+    <t>RC0402FR-07100KL</t>
+  </si>
+  <si>
+    <t>RC0603FR-0722K1L</t>
+  </si>
+  <si>
+    <t>RC0603FR-07220RL</t>
+  </si>
+  <si>
+    <t>RC0603FR-0747K5L</t>
+  </si>
+  <si>
+    <t>RC0603FR-0749R9L</t>
+  </si>
+  <si>
+    <t>RC0603FR-072R2L</t>
+  </si>
+  <si>
+    <t>RC0201FR-0722RL</t>
+  </si>
+  <si>
+    <t>RC0603JR-07120RL</t>
+  </si>
+  <si>
+    <t>AC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>RC0603JR-07330RL</t>
+  </si>
+  <si>
+    <t>RT0402BRD0712K1L</t>
+  </si>
+  <si>
+    <t>RC0201FR-0710KL</t>
+  </si>
+  <si>
+    <t>RC0603FR-0751RL</t>
+  </si>
+  <si>
+    <t>RC0603FR-0775RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-071KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-071ML</t>
+  </si>
+  <si>
+    <t>RC0402FR-07240RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07100RL</t>
+  </si>
+  <si>
+    <t>SKSTACE010</t>
+  </si>
+  <si>
+    <t>DSIC05LS-P</t>
+  </si>
+  <si>
+    <t>H1102NL</t>
+  </si>
+  <si>
+    <t>CP2102N-A02-GQFN28R</t>
+  </si>
+  <si>
+    <t>STM32G0B1RET6</t>
+  </si>
+  <si>
+    <t>MCP23017T-E/SS</t>
+  </si>
+  <si>
+    <t>ADS1115IDGSR</t>
+  </si>
+  <si>
+    <t>ESP32-WROOM-32E-N16</t>
+  </si>
+  <si>
+    <t>AP63300WU-7</t>
+  </si>
+  <si>
+    <t>BL8071CLATR33</t>
+  </si>
+  <si>
+    <t>TCAN1463DMTRQ1</t>
+  </si>
+  <si>
+    <t>PCF8574APWR</t>
+  </si>
+  <si>
+    <t>AT24C02C-SSHM-T</t>
+  </si>
+  <si>
+    <t>TXB0102DCUR</t>
+  </si>
+  <si>
+    <t>MAX3232ESE</t>
+  </si>
+  <si>
+    <t>THVD2450DRBR</t>
+  </si>
+  <si>
+    <t>LAN9253-I/R4X</t>
+  </si>
+  <si>
+    <t>KSZ8863RLLI</t>
+  </si>
+  <si>
+    <t>MC-306 32.7680K-A0:ROHS</t>
+  </si>
+  <si>
+    <t>5TJ480000XYLBC</t>
+  </si>
+  <si>
+    <t>X322525MRB4SI</t>
+  </si>
+  <si>
+    <t>ECS-2033-250-BN</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>Nichicon</t>
+  </si>
+  <si>
+    <t>Murata Electronics</t>
+  </si>
+  <si>
+    <t>ON Semiconductor</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>JSMSEMI</t>
+  </si>
+  <si>
+    <t>Diodes</t>
+  </si>
+  <si>
+    <t>Nexperia</t>
+  </si>
+  <si>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>RUILON</t>
+  </si>
+  <si>
+    <t>Korean Hroparts Elec</t>
+  </si>
+  <si>
+    <t>HCTL</t>
+  </si>
+  <si>
+    <t>BOOMELE</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>XKB</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>Littelfuse Wickmann</t>
+  </si>
+  <si>
+    <t>Phoenix Contact</t>
+  </si>
+  <si>
+    <t>XKB Connection</t>
+  </si>
+  <si>
+    <t>JUSHUO</t>
+  </si>
+  <si>
+    <t>DIBO</t>
+  </si>
+  <si>
+    <t>HANRUN</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>Sumida</t>
+  </si>
+  <si>
+    <t>Foshan NationStar Optoelectronics</t>
+  </si>
+  <si>
+    <t>FOSHAN Nationstar Optoelectronics</t>
+  </si>
+  <si>
+    <t>Jiangsu Changjing Electronics Technology</t>
+  </si>
+  <si>
+    <t>Slkor(SLKORMICRO Elec.)</t>
+  </si>
+  <si>
+    <t>YAGEO</t>
+  </si>
+  <si>
+    <t>Omron</t>
+  </si>
+  <si>
+    <t>Alps Electric</t>
+  </si>
+  <si>
+    <t>DongGuan KINGTEK Industrial Co.,LTD</t>
+  </si>
+  <si>
+    <t>XKB Connectivity</t>
+  </si>
+  <si>
+    <t>Pulse</t>
+  </si>
+  <si>
+    <t>Silicon Labs</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>Microchip</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>Espressif Systems</t>
+  </si>
+  <si>
+    <t>BL(Shanghai Belling)</t>
+  </si>
+  <si>
+    <t>UMW</t>
+  </si>
+  <si>
+    <t>Seiko Epson</t>
+  </si>
+  <si>
+    <t>JYJE</t>
+  </si>
+  <si>
+    <t>YXC</t>
+  </si>
+  <si>
+    <t>ECS International</t>
+  </si>
+  <si>
+    <t>4.7nF</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>4.7UF</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>30pF</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>47pF</t>
+  </si>
+  <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>0.1uf</t>
+  </si>
+  <si>
+    <t>470pF</t>
+  </si>
+  <si>
+    <t>10pF</t>
+  </si>
+  <si>
+    <t>1000pF</t>
+  </si>
+  <si>
+    <t>22nF</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>1nF</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>120R</t>
+  </si>
+  <si>
+    <t>68000-103HLF</t>
+  </si>
+  <si>
+    <t>6.8uH</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>5.1K</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>33R</t>
+  </si>
+  <si>
+    <t>158K</t>
+  </si>
+  <si>
+    <t>30.1K</t>
+  </si>
+  <si>
+    <t>3.9K</t>
+  </si>
+  <si>
+    <t>470R</t>
+  </si>
+  <si>
+    <t>200R</t>
+  </si>
+  <si>
+    <t>33K</t>
+  </si>
+  <si>
+    <t>60.4R</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>22.1K</t>
+  </si>
+  <si>
+    <t>220R</t>
+  </si>
+  <si>
+    <t>47.5K</t>
+  </si>
+  <si>
+    <t>49.9R</t>
+  </si>
+  <si>
+    <t>2.2R</t>
+  </si>
+  <si>
+    <t>22R</t>
+  </si>
+  <si>
+    <t>330R</t>
+  </si>
+  <si>
+    <t>12.1k</t>
+  </si>
+  <si>
+    <t>51R</t>
+  </si>
+  <si>
+    <t>75R</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>11.8K</t>
+  </si>
+  <si>
+    <t>240R</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>8MHz</t>
+  </si>
+  <si>
+    <t>25MHz</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Custom</t>
   </si>
   <si>
     <t>SOT-23-6</t>
   </si>
   <si>
-    <t>SOT- 223</t>
-  </si>
-  <si>
-    <t>VSON-14(3x4.5)</t>
-  </si>
-  <si>
-    <t>48-LQFP (7x7)_</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
-    <t>VSSOP-8(3.1x2.1)</t>
-  </si>
-  <si>
     <t>SO-Narrow-16</t>
   </si>
   <si>
-    <t>SON-8-EP(3x3)</t>
-  </si>
-  <si>
-    <t>QFN-64-EP(9x9)</t>
-  </si>
-  <si>
-    <t>CAT24C256WI-GT3</t>
-  </si>
-  <si>
-    <t>MC-306</t>
-  </si>
-  <si>
-    <t>SMD3225-4P</t>
-  </si>
-  <si>
-    <t>Q22FA12800090</t>
-  </si>
-  <si>
-    <t>Manufacturer Part Number</t>
-  </si>
-  <si>
-    <t>CC0603JRNPO9BN472</t>
-  </si>
-  <si>
-    <t>CC0603KRX5R7BB106</t>
-  </si>
-  <si>
-    <t>CC0402JRX7R7BB104</t>
-  </si>
-  <si>
-    <t>CC0402CRNPO9BN6R8</t>
-  </si>
-  <si>
-    <t>CC0402GRNPO9BN300</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R6BB475</t>
-  </si>
-  <si>
-    <t>C1005X7R1H104KT000F</t>
-  </si>
-  <si>
-    <t>C1005X5R1H104K050BB</t>
-  </si>
-  <si>
-    <t>GCM1555C1H470FA16D</t>
-  </si>
-  <si>
-    <t>UCD1H221MNL1GS</t>
-  </si>
-  <si>
-    <t>CC0603KRX5R7BB475</t>
-  </si>
-  <si>
-    <t>CC1206KKX5R9BB106</t>
-  </si>
-  <si>
-    <t>CC0805MKX5R8BB226</t>
-  </si>
-  <si>
-    <t>CC0402KRX7R9BB472</t>
-  </si>
-  <si>
-    <t>GRM155R62A104KE14D</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R7BB105</t>
-  </si>
-  <si>
-    <t>GRM155R11H471KA01D</t>
-  </si>
-  <si>
-    <t>GRM1555C1H100JA01D</t>
-  </si>
-  <si>
-    <t>C2012X5R1V226MT000E</t>
-  </si>
-  <si>
-    <t>0603B682K500NT</t>
-  </si>
-  <si>
-    <t>CC0603JRNPO9BN103</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB223</t>
-  </si>
-  <si>
-    <t>CC0603J*NPO9B*120</t>
-  </si>
-  <si>
-    <t>CC0603KRX5R6BB475</t>
-  </si>
-  <si>
-    <t>CC0402JRX7R7BB223</t>
-  </si>
-  <si>
-    <t>ESD9L5.0ST5G</t>
-  </si>
-  <si>
-    <t>SD03</t>
-  </si>
-  <si>
-    <t>MM3Z3V3</t>
-  </si>
-  <si>
-    <t>SS56</t>
-  </si>
-  <si>
-    <t>SMBJ28A-13-F</t>
-  </si>
-  <si>
-    <t>PESD5V0H1BSFYL</t>
-  </si>
-  <si>
-    <t>CDSOT23-T24CAN-Q</t>
-  </si>
-  <si>
-    <t>SM712</t>
-  </si>
-  <si>
-    <t>SMBJ8.0CA</t>
-  </si>
-  <si>
-    <t>MF-MSMF010-2</t>
-  </si>
-  <si>
-    <t>SMD0805P020TF</t>
-  </si>
-  <si>
-    <t>BLM18PG221SN1D</t>
-  </si>
-  <si>
-    <t>YI201209U301-2R0T</t>
-  </si>
-  <si>
-    <t>TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>C145963</t>
-  </si>
-  <si>
-    <t>X6511WV-09H-C60D30</t>
-  </si>
-  <si>
-    <t>X6511WV-05H-C60D30</t>
-  </si>
-  <si>
-    <t>X6511WV-04H-C60D30</t>
-  </si>
-  <si>
-    <t>B3B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>X6511WV-02H-C60D30</t>
-  </si>
-  <si>
-    <t>B4B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>BLM15AG601SN1D</t>
-  </si>
-  <si>
-    <t>0630CDMCCDS-6R8MC</t>
-  </si>
-  <si>
-    <t>NCD0603R3</t>
-  </si>
-  <si>
-    <t>NCD0603G2</t>
-  </si>
-  <si>
-    <t>LMUN2211LT1G</t>
-  </si>
-  <si>
-    <t>WPM2015-3/TR</t>
-  </si>
-  <si>
-    <t>BSS138</t>
-  </si>
-  <si>
-    <t>RC0402FR-075K1L</t>
-  </si>
-  <si>
-    <t>AF0402JR-071ML</t>
-  </si>
-  <si>
-    <t>RC0402FR-0710KL</t>
-  </si>
-  <si>
-    <t>RC0402FR-070RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-074K7L</t>
-  </si>
-  <si>
-    <t>RC0603JR-070RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-0733RL</t>
-  </si>
-  <si>
-    <t>RT0402BRE07158KL</t>
-  </si>
-  <si>
-    <t>RT0402BRD0730K1L</t>
-  </si>
-  <si>
-    <t>RC0402FR-073K9L</t>
-  </si>
-  <si>
-    <t>RC0402FR-07470RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-07200RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-0733KL</t>
-  </si>
-  <si>
-    <t>RTT0360R4FTP</t>
-  </si>
-  <si>
-    <t>RC0402FR-07100KL</t>
-  </si>
-  <si>
-    <t>CRCW04021K00FKEDHP</t>
-  </si>
-  <si>
-    <t>RC0603FR-0749R9L</t>
-  </si>
-  <si>
-    <t>CRCW040210R0FKEDHP</t>
-  </si>
-  <si>
-    <t>CRCW0402330RFKEDC</t>
-  </si>
-  <si>
-    <t>RC0603FR-0712K4L</t>
-  </si>
-  <si>
-    <t>RC0603FR-072R2L</t>
-  </si>
-  <si>
-    <t>RC0201FR-0722RL</t>
-  </si>
-  <si>
-    <t>RC0603JR-07120RL</t>
-  </si>
-  <si>
-    <t>AC0402FR-070RL</t>
-  </si>
-  <si>
-    <t>RC0603JR-07330RL</t>
-  </si>
-  <si>
-    <t>RT0402BRD0712K1L</t>
-  </si>
-  <si>
-    <t>RC0201FR-0710KL</t>
-  </si>
-  <si>
-    <t>RC0603FR-07220RL</t>
-  </si>
-  <si>
-    <t>SKSTACE010</t>
-  </si>
-  <si>
-    <t>ESP32-S3-WROOM-1-N16R8</t>
-  </si>
-  <si>
-    <t>STM32G0B1RET6</t>
-  </si>
-  <si>
-    <t>PCF8574APWR</t>
-  </si>
-  <si>
-    <t>ADS1115IDGSR</t>
-  </si>
-  <si>
-    <t>PCA9536D,118</t>
-  </si>
-  <si>
-    <t>AP63300WU-7</t>
-  </si>
-  <si>
-    <t>BL8071CLATR33</t>
-  </si>
-  <si>
-    <t>TCAN1463DMTRQ1</t>
-  </si>
-  <si>
-    <t>W5500</t>
-  </si>
-  <si>
-    <t>SP0504BAHTG</t>
-  </si>
-  <si>
-    <t>TXB0102DCUR</t>
-  </si>
-  <si>
-    <t>MAX3232ESE</t>
-  </si>
-  <si>
-    <t>THVD2450DRBR</t>
-  </si>
-  <si>
-    <t>LAN9253-I/R4X</t>
-  </si>
-  <si>
-    <t>MC-306 32.7680K-A0:ROHS</t>
-  </si>
-  <si>
-    <t>5TJ480000XYLBC</t>
-  </si>
-  <si>
-    <t>X322525MRB4SI</t>
-  </si>
-  <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>Yageo</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>Murata</t>
-  </si>
-  <si>
-    <t>Nichicon</t>
-  </si>
-  <si>
-    <t>Murata Electronics</t>
-  </si>
-  <si>
-    <t>TDK Corporation</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
-    <t>ON Semiconductor</t>
-  </si>
-  <si>
-    <t>MDD</t>
-  </si>
-  <si>
-    <t>JSMSEMI</t>
-  </si>
-  <si>
-    <t>Diodes</t>
-  </si>
-  <si>
-    <t>Nexperia</t>
-  </si>
-  <si>
-    <t>Bourns</t>
-  </si>
-  <si>
-    <t>TECH PUBLIC</t>
-  </si>
-  <si>
-    <t>Littelfuse</t>
-  </si>
-  <si>
-    <t>RUILON</t>
-  </si>
-  <si>
-    <t>YJYCOIN</t>
-  </si>
-  <si>
-    <t>Korean Hroparts Elec</t>
-  </si>
-  <si>
-    <t>HCTL</t>
-  </si>
-  <si>
-    <t>BOOMELE</t>
-  </si>
-  <si>
-    <t>XKB</t>
-  </si>
-  <si>
-    <t>JST</t>
-  </si>
-  <si>
-    <t>Littelfuse Wickmann</t>
-  </si>
-  <si>
-    <t>Phoenix Contact</t>
-  </si>
-  <si>
-    <t>XKB Connection</t>
-  </si>
-  <si>
-    <t>HANRUN</t>
-  </si>
-  <si>
-    <t>JUSHUO</t>
-  </si>
-  <si>
-    <t>DIBO</t>
-  </si>
-  <si>
-    <t>XFCN</t>
-  </si>
-  <si>
-    <t>Sumida</t>
-  </si>
-  <si>
-    <t>Foshan NationStar Optoelectronics</t>
-  </si>
-  <si>
-    <t>LRC</t>
-  </si>
-  <si>
-    <t>WILLSEMI</t>
-  </si>
-  <si>
-    <t>Slkor(SLKORMICRO Elec.)</t>
-  </si>
-  <si>
-    <t>YAGEO</t>
-  </si>
-  <si>
-    <t>Vishay Dale</t>
-  </si>
-  <si>
-    <t>Vishay Semiconductors</t>
-  </si>
-  <si>
-    <t>Omron</t>
-  </si>
-  <si>
-    <t>Alps Electric</t>
-  </si>
-  <si>
-    <t>DongGuan KINGTEK Industrial Co.,LTD</t>
-  </si>
-  <si>
-    <t>Espressif Systems</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
-    <t>NXP Semiconductors</t>
-  </si>
-  <si>
-    <t>BL(Shanghai Belling)</t>
-  </si>
-  <si>
-    <t>WIZNET</t>
-  </si>
-  <si>
-    <t>UMW</t>
-  </si>
-  <si>
-    <t>Microchip</t>
-  </si>
-  <si>
-    <t>Seiko Epson</t>
-  </si>
-  <si>
-    <t>JYJE</t>
-  </si>
-  <si>
-    <t>YXC</t>
-  </si>
-  <si>
-    <t>4.7nF</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
-    <t>DNP</t>
-  </si>
-  <si>
-    <t>30pF</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>47pF</t>
-  </si>
-  <si>
-    <t>220uF</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>0.1uf</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>470pF</t>
-  </si>
-  <si>
-    <t>10pF</t>
-  </si>
-  <si>
-    <t>6.8nF</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>22nF</t>
-  </si>
-  <si>
-    <t>12pF</t>
-  </si>
-  <si>
-    <t>100MHz</t>
-  </si>
-  <si>
-    <t>68000-103HLF</t>
-  </si>
-  <si>
-    <t>6.8uH</t>
-  </si>
-  <si>
-    <t>5.1K</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>0R</t>
-  </si>
-  <si>
-    <t>33R</t>
-  </si>
-  <si>
-    <t>158K</t>
-  </si>
-  <si>
-    <t>30.1K</t>
-  </si>
-  <si>
-    <t>3.9K</t>
-  </si>
-  <si>
-    <t>470R</t>
-  </si>
-  <si>
-    <t>200R</t>
-  </si>
-  <si>
-    <t>33K</t>
-  </si>
-  <si>
-    <t>60.4R</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>49.9R</t>
-  </si>
-  <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>330R</t>
-  </si>
-  <si>
-    <t>12.4K</t>
-  </si>
-  <si>
-    <t>2.2R</t>
-  </si>
-  <si>
-    <t>22R</t>
-  </si>
-  <si>
-    <t>120R</t>
-  </si>
-  <si>
-    <t>12.1k</t>
-  </si>
-  <si>
-    <t>220R</t>
-  </si>
-  <si>
-    <t>8MHz</t>
-  </si>
-  <si>
-    <t>25MHz</t>
-  </si>
-  <si>
-    <t>Quantity</t>
+    <t>Ralec</t>
+  </si>
+  <si>
+    <t>DO NOT PLACE</t>
+  </si>
+  <si>
+    <t>RC0402FR-072KL</t>
   </si>
   <si>
     <t>Amphenol</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>DO NOT PLACE</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>RT0603BRD0711K8L</t>
   </si>
   <si>
     <t>Peripheral</t>
@@ -1599,58 +1758,49 @@
     <t>3.5" inch 320*480 32P/0.5 ST7796 8/16 MCU Parallel 3/4 SPI TFT Color LCD Module Display Screen Resistive Capacitive Touch Panel</t>
   </si>
   <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
     <t>Jumper</t>
   </si>
   <si>
     <t>P=2.54mm Shunts, Jumpers ROHS</t>
   </si>
   <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 2A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>SSD1315 I2C 128x64 0.96 OLED Display ROHS</t>
+  </si>
+  <si>
+    <t>CS-IPS-ST7796-NTP</t>
+  </si>
+  <si>
+    <t>---------</t>
+  </si>
+  <si>
     <t>X2541-A1NIB</t>
   </si>
   <si>
-    <t>Ethernet Cable</t>
-  </si>
-  <si>
-    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
-  </si>
-  <si>
     <t xml:space="preserve">UGREEN </t>
   </si>
   <si>
-    <t>TFT Module</t>
-  </si>
-  <si>
-    <t>32V 1kA Blade fuse 2A Automotive Fuses ROHS</t>
-  </si>
-  <si>
     <t>0287002.PXCN</t>
   </si>
   <si>
     <t xml:space="preserve">Littelfuse </t>
   </si>
   <si>
-    <t>OLED</t>
-  </si>
-  <si>
-    <t>SSD1315 I2C 128x64 0.96 OLED Display ROHS</t>
-  </si>
-  <si>
     <t>HS96L03W2C03</t>
   </si>
   <si>
     <t xml:space="preserve">HS </t>
-  </si>
-  <si>
-    <t>CS-IPS-ST7796-NTP</t>
-  </si>
-  <si>
-    <t>LED4, LED6</t>
-  </si>
-  <si>
-    <t>R89</t>
   </si>
 </sst>
 </file>
@@ -1718,9 +1868,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1838,11 +1987,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1879,42 +2027,26 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2200,25 +2332,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R125"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2227,14 +2356,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="23"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2243,31 +2369,31 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>519</v>
+        <v>459</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>566</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>517</v>
+        <v>565</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -2277,93 +2403,93 @@
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B120" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B132" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>471</v>
+        <v>461</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>511</v>
       </c>
       <c r="J4" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>472</v>
+        <v>461</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>512</v>
       </c>
       <c r="J5" s="7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -2372,128 +2498,128 @@
       <c r="C6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>36</v>
+      <c r="D6" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>263</v>
+        <v>169</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>294</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>419</v>
+        <v>353</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>460</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="J6" s="14">
+        <v>513</v>
+      </c>
+      <c r="J6" s="16">
         <v>2</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>474</v>
+        <v>460</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>511</v>
       </c>
       <c r="J7" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>263</v>
+        <v>171</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>475</v>
+        <v>460</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>514</v>
       </c>
       <c r="J8" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:15" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>264</v>
+        <v>172</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>294</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>476</v>
+        <v>460</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>515</v>
       </c>
       <c r="J9" s="7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -2503,29 +2629,29 @@
         <v>2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>263</v>
+        <v>173</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>295</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>472</v>
+        <v>462</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>516</v>
       </c>
       <c r="J10" s="9">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -2535,29 +2661,29 @@
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>477</v>
+        <v>460</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>517</v>
       </c>
       <c r="J11" s="7">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -2567,153 +2693,153 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="J12" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
         <v>11</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="J13" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="J14" s="9">
         <v>3</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="J14" s="9">
-        <v>1</v>
-      </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>479</v>
+        <v>515</v>
       </c>
       <c r="J15" s="7">
         <v>3</v>
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>470</v>
+        <v>520</v>
       </c>
       <c r="J16" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="9"/>
     </row>
@@ -2727,25 +2853,25 @@
         <v>2</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="J17" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K17" s="7"/>
     </row>
@@ -2759,29 +2885,29 @@
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>481</v>
+        <v>460</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>520</v>
       </c>
       <c r="J18" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -2791,25 +2917,25 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>263</v>
+        <v>182</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>294</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>482</v>
+        <v>460</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>510</v>
       </c>
       <c r="J19" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="7"/>
     </row>
@@ -2823,29 +2949,29 @@
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>263</v>
+        <v>183</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>483</v>
+        <v>463</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>522</v>
       </c>
       <c r="J20" s="9">
         <v>8</v>
       </c>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
@@ -2855,22 +2981,22 @@
         <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>424</v>
+        <v>465</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>479</v>
+        <v>523</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2887,25 +3013,25 @@
         <v>2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>484</v>
+        <v>524</v>
       </c>
       <c r="J22" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K22" s="9"/>
     </row>
@@ -2919,22 +3045,22 @@
         <v>2</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>485</v>
+        <v>460</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>525</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -2951,25 +3077,25 @@
         <v>2</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>262</v>
+        <v>187</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>486</v>
+        <v>460</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>526</v>
       </c>
       <c r="J24" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="9"/>
     </row>
@@ -2983,25 +3109,25 @@
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>487</v>
+        <v>460</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>527</v>
       </c>
       <c r="J25" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="7"/>
     </row>
@@ -3015,22 +3141,22 @@
         <v>2</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>475</v>
+        <v>460</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>528</v>
       </c>
       <c r="J26" s="9">
         <v>1</v>
@@ -3047,25 +3173,25 @@
         <v>2</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>486</v>
+        <v>460</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>529</v>
       </c>
       <c r="J27" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="7"/>
     </row>
@@ -3076,124 +3202,126 @@
         <v>26</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="J28" s="9">
-        <v>4</v>
-      </c>
-      <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J28" s="16">
+        <v>2</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="J29" s="7">
         <v>4</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="J29" s="7">
-        <v>2</v>
-      </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>269</v>
+        <v>193</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J30" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>270</v>
+        <v>194</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>300</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J31" s="7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -3203,26 +3331,26 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>271</v>
+        <v>195</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -3239,25 +3367,25 @@
         <v>5</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>272</v>
+        <v>196</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>302</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J33" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -3268,25 +3396,25 @@
         <v>32</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>273</v>
+        <v>197</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J34" s="9">
         <v>2</v>
@@ -3300,28 +3428,28 @@
         <v>33</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>273</v>
+        <v>198</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>304</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J35" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" s="7"/>
     </row>
@@ -3332,60 +3460,60 @@
         <v>34</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>274</v>
+        <v>199</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J36" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f>ROW(B37) - ROW($B$2)</f>
         <v>35</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>275</v>
+        <v>200</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>431</v>
+        <v>473</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J37" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K37" s="7"/>
     </row>
@@ -3399,61 +3527,61 @@
         <v>7</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>276</v>
+        <v>201</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J38" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K38" s="9"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
         <v>37</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>277</v>
+        <v>202</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>307</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>421</v>
+        <v>474</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J39" s="7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
@@ -3463,150 +3591,150 @@
         <v>8</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>278</v>
+        <v>203</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>488</v>
+        <v>567</v>
       </c>
       <c r="J40" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>521</v>
+        <v>308</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>523</v>
+        <v>465</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>530</v>
       </c>
       <c r="J41" s="7">
         <v>2</v>
       </c>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>279</v>
+        <v>389</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J42" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f>ROW(B43) - ROW($B$2)</f>
         <v>41</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J43" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>280</v>
+        <v>207</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
@@ -3623,25 +3751,25 @@
         <v>12</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>281</v>
+        <v>569</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>489</v>
+        <v>310</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>523</v>
+        <v>478</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="J45" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" s="7"/>
     </row>
@@ -3652,96 +3780,96 @@
         <v>44</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>523</v>
+        <v>479</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="J46" s="9">
         <v>1</v>
       </c>
       <c r="K46" s="9"/>
     </row>
-    <row r="47" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>361</v>
+        <v>312</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>531</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>439</v>
+        <v>575</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J47" s="7">
         <v>1</v>
       </c>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>521</v>
+        <v>211</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>313</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J48" s="9">
         <v>1</v>
       </c>
       <c r="K48" s="9"/>
     </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f>ROW(B49) - ROW($B$2)</f>
@@ -3751,22 +3879,22 @@
         <v>13</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>521</v>
+        <v>314</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>284</v>
+        <v>393</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
@@ -3780,64 +3908,64 @@
         <v>48</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G50" s="10">
-        <v>1715721</v>
+        <v>569</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>394</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J50" s="9">
         <v>1</v>
       </c>
       <c r="K50" s="9"/>
     </row>
-    <row r="51" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>285</v>
+        <v>569</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>363</v>
+        <v>315</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J51" s="7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f t="shared" si="0"/>
@@ -3847,283 +3975,285 @@
         <v>15</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>286</v>
+        <v>569</v>
+      </c>
+      <c r="G52" s="10">
+        <v>1715721</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J52" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" s="9"/>
     </row>
-    <row r="53" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>521</v>
+        <v>316</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>287</v>
+        <v>395</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J53" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J54" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="9"/>
     </row>
-    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
       </c>
       <c r="K55" s="7"/>
     </row>
-    <row r="56" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>289</v>
+        <v>396</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J56" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K56" s="9"/>
     </row>
-    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f>ROW(B57) - ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="12"/>
+      <c r="C57" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="D57" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J57" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>291</v>
+        <v>221</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>523</v>
+        <v>486</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>320</v>
       </c>
       <c r="J58" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f>ROW(B59) - ROW($B$2)</f>
         <v>57</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>490</v>
+        <v>567</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
       </c>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>523</v>
+        <v>463</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>567</v>
       </c>
       <c r="J60" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K60" s="9"/>
     </row>
-    <row r="61" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f>ROW(B61) - ROW($B$2)</f>
@@ -4133,25 +4263,25 @@
         <v>20</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>542</v>
+        <v>92</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>292</v>
+        <v>569</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>523</v>
+        <v>488</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>532</v>
       </c>
       <c r="J61" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="7"/>
     </row>
@@ -4165,29 +4295,29 @@
         <v>21</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J62" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K62" s="9"/>
     </row>
-    <row r="63" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f>ROW(B63) - ROW($B$2)</f>
@@ -4197,29 +4327,29 @@
         <v>21</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J63" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="7"/>
     </row>
-    <row r="64" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="0"/>
@@ -4229,93 +4359,93 @@
         <v>21</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="I64" s="10" t="s">
-        <v>523</v>
+        <v>490</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>401</v>
       </c>
       <c r="J64" s="9">
         <v>1</v>
       </c>
       <c r="K64" s="9"/>
     </row>
-    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f>ROW(B65) - ROW($B$2)</f>
         <v>63</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>491</v>
+        <v>489</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>533</v>
       </c>
       <c r="J65" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="12" t="s">
         <v>22</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I66" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>403</v>
       </c>
       <c r="J66" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f>ROW(B67) - ROW($B$2)</f>
@@ -4325,30 +4455,30 @@
         <v>22</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>294</v>
+        <v>230</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>324</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I67" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>567</v>
       </c>
       <c r="J67" s="7">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:18" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="19"/>
+    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -4356,944 +4486,928 @@
       <c r="C68" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="G68" s="15" t="s">
-        <v>375</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="I68" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="J68" s="14">
-        <v>2</v>
-      </c>
-      <c r="K68" s="16" t="s">
-        <v>522</v>
-      </c>
-      <c r="M68"/>
-      <c r="N68"/>
-      <c r="O68"/>
-      <c r="P68"/>
-      <c r="Q68"/>
-      <c r="R68"/>
-    </row>
-    <row r="69" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="J68" s="9">
+        <v>7</v>
+      </c>
+      <c r="K68" s="9"/>
+    </row>
+    <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f>ROW(B69) - ROW($B$2)</f>
         <v>67</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>294</v>
+        <v>232</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>494</v>
+        <v>460</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>535</v>
       </c>
       <c r="J69" s="7">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" spans="1:18" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="19"/>
+    <row r="70" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="F70" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="G70" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="I70" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="J70" s="14">
-        <v>2</v>
-      </c>
-      <c r="K70" s="16" t="s">
-        <v>522</v>
-      </c>
-      <c r="M70"/>
-      <c r="N70"/>
-      <c r="O70"/>
-      <c r="P70"/>
-      <c r="Q70"/>
-      <c r="R70"/>
-    </row>
-    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="J70" s="9">
+        <v>42</v>
+      </c>
+      <c r="K70" s="9"/>
+    </row>
+    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="11">
         <f>ROW(B71) - ROW($B$2)</f>
         <v>69</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>377</v>
+        <v>325</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>574</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>495</v>
+        <v>460</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>537</v>
       </c>
       <c r="J71" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I72" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="J72" s="9">
-        <v>13</v>
-      </c>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="73" spans="1:18" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J72" s="16">
+        <v>3</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
         <f>ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>495</v>
+        <v>538</v>
       </c>
       <c r="J73" s="7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K73" s="7"/>
     </row>
-    <row r="74" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="11">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I74" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="J74" s="9">
-        <v>1</v>
-      </c>
-      <c r="K74" s="9"/>
-    </row>
-    <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I74" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J74" s="16">
+        <v>2</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="11">
         <f>ROW(B75) - ROW($B$2)</f>
         <v>73</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="J75" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="11">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>22</v>
+      <c r="C76" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="J76" s="9">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="11">
         <f>ROW(B77) - ROW($B$2)</f>
         <v>75</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="J77" s="7">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="11">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>22</v>
+      <c r="C78" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>501</v>
+        <v>541</v>
       </c>
       <c r="J78" s="9">
         <v>1</v>
       </c>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="11">
         <f>ROW(B79) - ROW($B$2)</f>
         <v>77</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>502</v>
+        <v>542</v>
       </c>
       <c r="J79" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C80" s="12" t="s">
-        <v>22</v>
+      <c r="C80" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="H80" s="9"/>
+        <v>414</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>460</v>
+      </c>
       <c r="I80" s="10" t="s">
-        <v>503</v>
+        <v>543</v>
       </c>
       <c r="J80" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f>ROW(B81) - ROW($B$2)</f>
         <v>79</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>504</v>
+        <v>544</v>
       </c>
       <c r="J81" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="7"/>
     </row>
-    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="11">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>505</v>
+        <v>545</v>
       </c>
       <c r="J82" s="9">
         <v>1</v>
       </c>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="11">
         <f>ROW(B83) - ROW($B$2)</f>
         <v>81</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>419</v>
+        <v>493</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>506</v>
+        <v>546</v>
       </c>
       <c r="J83" s="7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K83" s="7"/>
     </row>
-    <row r="84" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="11">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>454</v>
+        <v>572</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>507</v>
+        <v>547</v>
       </c>
       <c r="J84" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="11">
         <f>ROW(B85) - ROW($B$2)</f>
         <v>83</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>508</v>
+        <v>548</v>
       </c>
       <c r="J85" s="7">
         <v>2</v>
       </c>
       <c r="K85" s="7"/>
     </row>
-    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I86" s="10" t="s">
-        <v>509</v>
+        <v>460</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>549</v>
       </c>
       <c r="J86" s="9">
         <v>1</v>
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B87) - ROW($B$2)</f>
         <v>85</v>
       </c>
-      <c r="C87" s="13" t="s">
-        <v>22</v>
+      <c r="C87" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>543</v>
+        <v>118</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I87" s="8" t="s">
-        <v>514</v>
+        <v>460</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>550</v>
       </c>
       <c r="J87" s="7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
-        <f>ROW(B88) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D88" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I88" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="J88" s="7">
-        <v>1</v>
-      </c>
-      <c r="K88" s="7"/>
-    </row>
-    <row r="89" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D88" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="J88" s="9">
+        <v>1</v>
+      </c>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B89) - ROW($B$2)</f>
         <v>87</v>
       </c>
-      <c r="C89" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I89" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="J89" s="9">
-        <v>10</v>
-      </c>
-      <c r="K89" s="9"/>
-    </row>
-    <row r="90" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C89" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="J89" s="7">
+        <v>23</v>
+      </c>
+      <c r="K89" s="7"/>
+    </row>
+    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
-        <f>ROW(B90) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="J90" s="7">
-        <v>3</v>
-      </c>
-      <c r="K90" s="7"/>
-    </row>
-    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C90" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="H90" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I90" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J90" s="16">
+        <v>2</v>
+      </c>
+      <c r="K90" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B91) - ROW($B$2)</f>
         <v>89</v>
       </c>
-      <c r="C91" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I91" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="J91" s="9">
-        <v>2</v>
-      </c>
-      <c r="K91" s="9"/>
-    </row>
-    <row r="92" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="J91" s="7">
+        <v>1</v>
+      </c>
+      <c r="K91" s="7"/>
+    </row>
+    <row r="92" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
-        <f>ROW(B92) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="I92" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="J92" s="7">
-        <v>4</v>
-      </c>
-      <c r="K92" s="7"/>
-    </row>
-    <row r="93" spans="1:18" s="20" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="19"/>
+      <c r="C92" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="J92" s="9">
+        <v>10</v>
+      </c>
+      <c r="K92" s="9"/>
+    </row>
+    <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
       <c r="B93" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B93) - ROW($B$2)</f>
         <v>91</v>
       </c>
-      <c r="C93" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I93" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="J93" s="9">
-        <v>1</v>
-      </c>
-      <c r="K93" s="9"/>
-      <c r="M93"/>
-      <c r="N93"/>
-      <c r="O93"/>
-      <c r="P93"/>
-      <c r="Q93"/>
-      <c r="R93"/>
-    </row>
-    <row r="94" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C93" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="J93" s="7">
+        <v>3</v>
+      </c>
+      <c r="K93" s="7"/>
+    </row>
+    <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="11">
-        <f>ROW(B94) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="C94" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D94" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="F94" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="G94" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="H94" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="I94" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="J94" s="17">
-        <v>1</v>
-      </c>
-      <c r="K94" s="16" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="J94" s="9">
+        <v>2</v>
+      </c>
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B95) - ROW($B$2)</f>
         <v>93</v>
       </c>
-      <c r="C95" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I95" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="J95" s="9">
-        <v>1</v>
-      </c>
-      <c r="K95" s="9"/>
-    </row>
-    <row r="96" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C95" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="J95" s="7">
+        <v>4</v>
+      </c>
+      <c r="K95" s="7"/>
+    </row>
+    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="11">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>521</v>
+        <v>325</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>297</v>
+        <v>429</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>493</v>
+        <v>556</v>
       </c>
       <c r="J96" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K96" s="9"/>
     </row>
@@ -5304,92 +5418,94 @@
         <v>95</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="J97" s="7">
-        <v>3</v>
-      </c>
-      <c r="K97" s="7"/>
-    </row>
-    <row r="98" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F97" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="H97" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J97" s="16">
+        <v>1</v>
+      </c>
+      <c r="K97" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="11">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="C98" s="12" t="s">
-        <v>25</v>
+      <c r="C98" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>521</v>
+        <v>327</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>523</v>
+        <v>460</v>
+      </c>
+      <c r="I98" s="10" t="s">
+        <v>536</v>
       </c>
       <c r="J98" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f>ROW(B99) - ROW($B$2)</f>
         <v>97</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>521</v>
+        <v>258</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>523</v>
+        <v>460</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>557</v>
       </c>
       <c r="J99" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K99" s="7"/>
     </row>
@@ -5400,60 +5516,60 @@
         <v>98</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>523</v>
+        <v>460</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>558</v>
       </c>
       <c r="J100" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" s="9"/>
     </row>
-    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
         <f>ROW(B101) - ROW($B$2)</f>
         <v>99</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="H101" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="I101" s="8" t="s">
-        <v>523</v>
+      <c r="I101" s="7" t="s">
+        <v>559</v>
       </c>
       <c r="J101" s="7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K101" s="7"/>
     </row>
@@ -5463,26 +5579,26 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="C102" s="13" t="s">
-        <v>29</v>
+      <c r="C102" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="I102" s="8" t="s">
-        <v>523</v>
+        <v>326</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>560</v>
       </c>
       <c r="J102" s="9">
         <v>1</v>
@@ -5496,30 +5612,32 @@
         <v>101</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>523</v>
+        <v>23</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="H103" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I103" s="15" t="s">
+        <v>513</v>
       </c>
       <c r="J103" s="7">
         <v>1</v>
       </c>
-      <c r="K103" s="7"/>
+      <c r="K103" s="17" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
@@ -5528,30 +5646,32 @@
         <v>102</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>523</v>
+        <v>23</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="H104" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>513</v>
       </c>
       <c r="J104" s="9">
         <v>1</v>
       </c>
-      <c r="K104" s="9"/>
+      <c r="K104" s="17" t="s">
+        <v>573</v>
+      </c>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
@@ -5560,57 +5680,57 @@
         <v>103</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>406</v>
+        <v>435</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>523</v>
+        <v>460</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>561</v>
       </c>
       <c r="J105" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K105" s="7"/>
     </row>
-    <row r="106" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="11">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>523</v>
+        <v>460</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>562</v>
       </c>
       <c r="J106" s="9">
         <v>1</v>
@@ -5624,153 +5744,153 @@
         <v>105</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>307</v>
+        <v>265</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J107" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K107" s="7"/>
     </row>
-    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="C108" s="13" t="s">
-        <v>29</v>
+      <c r="C108" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>308</v>
+        <v>569</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J108" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K108" s="9"/>
     </row>
-    <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="11">
         <f>ROW(B109) - ROW($B$2)</f>
         <v>107</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>309</v>
+        <v>267</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>410</v>
+        <v>329</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>433</v>
+        <v>496</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J109" s="7">
         <v>1</v>
       </c>
       <c r="K109" s="7"/>
     </row>
-    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="11">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>310</v>
+        <v>569</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J110" s="9">
         <v>1</v>
       </c>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="11">
         <f>ROW(B111) - ROW($B$2)</f>
         <v>109</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>311</v>
+        <v>269</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J111" s="7">
         <v>1</v>
@@ -5784,57 +5904,57 @@
         <v>110</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>312</v>
+        <v>569</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>523</v>
+        <v>498</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="J112" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
         <f>ROW(B113) - ROW($B$2)</f>
         <v>111</v>
       </c>
-      <c r="C113" s="12" t="s">
-        <v>29</v>
+      <c r="C113" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="I113" s="8" t="s">
-        <v>523</v>
+        <v>499</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="J113" s="7">
         <v>1</v>
@@ -5851,120 +5971,118 @@
         <v>29</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>521</v>
+        <v>272</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>332</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>314</v>
+        <v>441</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>426</v>
+        <v>500</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="J114" s="9">
         <v>1</v>
       </c>
       <c r="K114" s="9"/>
     </row>
-    <row r="115" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="11">
         <f>ROW(B115) - ROW($B$2)</f>
         <v>113</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="E115" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="F115" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="G115" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="H115" s="14" t="s">
-        <v>467</v>
-      </c>
-      <c r="I115" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="J115" s="14">
-        <v>1</v>
-      </c>
-      <c r="K115" s="16" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="J115" s="7">
+        <v>1</v>
+      </c>
+      <c r="K115" s="7"/>
+    </row>
+    <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="11">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>521</v>
+        <v>274</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>515</v>
+        <v>502</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>567</v>
       </c>
       <c r="J116" s="9">
         <v>1</v>
       </c>
       <c r="K116" s="9"/>
     </row>
-    <row r="117" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="11">
         <f>ROW(B117) - ROW($B$2)</f>
         <v>115</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>516</v>
+        <v>503</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="J117" s="7">
         <v>1</v>
@@ -5978,204 +6096,675 @@
         <v>116</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>521</v>
+        <v>276</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>570</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>317</v>
+        <v>445</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="I118" s="10" t="s">
-        <v>516</v>
+        <v>469</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>567</v>
       </c>
       <c r="J118" s="9">
         <v>1</v>
       </c>
       <c r="K118" s="9"/>
     </row>
-    <row r="119" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1"/>
       <c r="B119" s="11">
-        <f t="shared" si="0"/>
+        <f>ROW(B119) - ROW($B$2)</f>
         <v>117</v>
       </c>
-      <c r="C119" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="E119" s="9" t="s">
-        <v>525</v>
+      <c r="C119" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="I119" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="J119" s="9">
-        <v>1</v>
-      </c>
-      <c r="K119" s="22" t="s">
-        <v>526</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J119" s="7">
+        <v>1</v>
+      </c>
+      <c r="K119" s="7"/>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1"/>
       <c r="B120" s="11">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="C120" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>528</v>
+      <c r="C120" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="I120" s="21" t="s">
-        <v>523</v>
+        <v>337</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>567</v>
       </c>
       <c r="J120" s="9">
+        <v>2</v>
+      </c>
+      <c r="K120" s="9"/>
+    </row>
+    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="1"/>
+      <c r="B121" s="11">
+        <f>ROW(B121) - ROW($B$2)</f>
+        <v>119</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="J121" s="7">
+        <v>1</v>
+      </c>
+      <c r="K121" s="7"/>
+    </row>
+    <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1"/>
+      <c r="B122" s="11">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="J122" s="9">
+        <v>1</v>
+      </c>
+      <c r="K122" s="9"/>
+    </row>
+    <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="1"/>
+      <c r="B123" s="11">
+        <f>ROW(B123) - ROW($B$2)</f>
+        <v>121</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J123" s="7">
+        <v>1</v>
+      </c>
+      <c r="K123" s="7"/>
+    </row>
+    <row r="124" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="1"/>
+      <c r="B124" s="11">
+        <f t="shared" si="0"/>
+        <v>122</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J124" s="9">
+        <v>1</v>
+      </c>
+      <c r="K124" s="9"/>
+    </row>
+    <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="1"/>
+      <c r="B125" s="11">
+        <f>ROW(B125) - ROW($B$2)</f>
+        <v>123</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J125" s="7">
+        <v>3</v>
+      </c>
+      <c r="K125" s="7"/>
+    </row>
+    <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1"/>
+      <c r="B126" s="11">
+        <f t="shared" si="0"/>
+        <v>124</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J126" s="9">
+        <v>1</v>
+      </c>
+      <c r="K126" s="9"/>
+    </row>
+    <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="1"/>
+      <c r="B127" s="11">
+        <f>ROW(B127) - ROW($B$2)</f>
+        <v>125</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J127" s="7">
+        <v>1</v>
+      </c>
+      <c r="K127" s="7"/>
+    </row>
+    <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1"/>
+      <c r="B128" s="11">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="J128" s="9">
+        <v>1</v>
+      </c>
+      <c r="K128" s="9"/>
+    </row>
+    <row r="129" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1"/>
+      <c r="B129" s="11">
+        <f>ROW(B129) - ROW($B$2)</f>
+        <v>127</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E129" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="F129" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="G129" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="H129" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="I129" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J129" s="7">
+        <v>1</v>
+      </c>
+      <c r="K129" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1"/>
+      <c r="B130" s="11">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="J130" s="9">
+        <v>1</v>
+      </c>
+      <c r="K130" s="9"/>
+    </row>
+    <row r="131" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1"/>
+      <c r="B131" s="11">
+        <f>ROW(B131) - ROW($B$2)</f>
+        <v>129</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="J131" s="7">
+        <v>1</v>
+      </c>
+      <c r="K131" s="7"/>
+    </row>
+    <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1"/>
+      <c r="B132" s="11">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="J132" s="9">
+        <v>1</v>
+      </c>
+      <c r="K132" s="9"/>
+    </row>
+    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1"/>
+      <c r="B133" s="11">
+        <f>ROW(B133) - ROW($B$2)</f>
+        <v>131</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E133" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="F133" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="G133" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="H133" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="I133" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="J133" s="7">
+        <v>1</v>
+      </c>
+      <c r="K133" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B134" s="11">
+        <f t="shared" ref="B134:B138" si="1">ROW(B134) - ROW($B$2)</f>
+        <v>132</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="I134" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="J134" s="9">
+        <v>1</v>
+      </c>
+      <c r="K134" s="7"/>
+    </row>
+    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B135" s="11">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="I135" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="J135" s="9">
         <v>8</v>
       </c>
-      <c r="K120" s="22"/>
-    </row>
-    <row r="121" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="11">
-        <f t="shared" ref="B121:B123" si="1">ROW(B121) - ROW($B$2)</f>
-        <v>119</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G121" s="8">
+      <c r="K135" s="7"/>
+    </row>
+    <row r="136" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="11">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G136" s="8">
         <v>50173</v>
       </c>
-      <c r="H121" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I121" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="J121" s="9">
+      <c r="H136" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="I136" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="J136" s="9">
         <v>2</v>
       </c>
-      <c r="K121" s="22"/>
-    </row>
-    <row r="122" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="11">
+      <c r="K136" s="7"/>
+    </row>
+    <row r="137" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B137" s="11">
         <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="C122" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="D122" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="D137" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G122" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="I122" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="J122" s="9">
-        <v>1</v>
-      </c>
-      <c r="K122" s="22"/>
-    </row>
-    <row r="123" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="11">
+      <c r="E137" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="I137" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="J137" s="9">
+        <v>1</v>
+      </c>
+      <c r="K137" s="7"/>
+    </row>
+    <row r="138" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B138" s="11">
         <f t="shared" si="1"/>
-        <v>121</v>
-      </c>
-      <c r="C123" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="I123" s="21" t="s">
-        <v>523</v>
-      </c>
-      <c r="J123" s="9">
-        <v>1</v>
-      </c>
-      <c r="K123" s="22"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B124"/>
-      <c r="C124"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B125"/>
-      <c r="C125"/>
+        <v>136</v>
+      </c>
+      <c r="C138" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="I138" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="J138" s="9">
+        <v>1</v>
+      </c>
+      <c r="K138" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="K119" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>